--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\images\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449CDE3E-3CDA-48A6-99FC-0348141BBDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161112AB-E90D-4142-9FCC-A173D57155C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -91,7 +91,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -424,12 +424,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
   <dimension ref="B2:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -440,7 +441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -459,12 +460,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
   <dimension ref="B2:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -475,7 +477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161112AB-E90D-4142-9FCC-A173D57155C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E9A8F4-0A9D-4734-9016-14B2CFB67A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="6">
   <si>
     <t>Datum</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>USB Treiber 💀</t>
+  </si>
+  <si>
+    <t>proto-sequencer firmware</t>
   </si>
 </sst>
 </file>
@@ -87,8 +90,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -423,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B2:D3"/>
+  <dimension ref="B2:D6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -450,6 +454,39 @@
       </c>
       <c r="D3" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B4" s="1">
+        <v>45891</v>
+      </c>
+      <c r="C4">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B5" s="1">
+        <v>45892</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B6" s="1">
+        <v>45893</v>
+      </c>
+      <c r="C6">
+        <v>0.5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E9A8F4-0A9D-4734-9016-14B2CFB67A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3749A8-8D9B-4383-A05F-14DEC481C560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="7">
   <si>
     <t>Datum</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>proto-sequencer firmware</t>
+  </si>
+  <si>
+    <t>sequencer</t>
   </si>
 </sst>
 </file>
@@ -427,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B2:D6"/>
+  <dimension ref="B2:D7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -487,6 +490,17 @@
       </c>
       <c r="D6" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" s="1">
+        <v>45894</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3749A8-8D9B-4383-A05F-14DEC481C560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A053EB-104D-479F-83FC-028923C4D238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
   <si>
     <t>Datum</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>sequencer</t>
+  </si>
+  <si>
+    <t>sequencer pcb</t>
   </si>
 </sst>
 </file>
@@ -430,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B2:D7"/>
+  <dimension ref="B2:D8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -501,6 +504,17 @@
       </c>
       <c r="D7" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B8" s="1">
+        <v>45896</v>
+      </c>
+      <c r="C8">
+        <v>1.5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A053EB-104D-479F-83FC-028923C4D238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE36C4F9-E732-423F-82AB-6F1E46D2D7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
   <si>
     <t>Datum</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>sequencer pcb</t>
+  </si>
+  <si>
+    <t>io unit schematic and pcb</t>
+  </si>
+  <si>
+    <t>frontpanel schematic and pcb</t>
   </si>
 </sst>
 </file>
@@ -433,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B2:D8"/>
+  <dimension ref="B2:D10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -515,6 +521,28 @@
       </c>
       <c r="D8" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B9" s="1">
+        <v>45897</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B10" s="1">
+        <v>45897</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE36C4F9-E732-423F-82AB-6F1E46D2D7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6227DB57-67EF-4ABD-A492-F028E2482F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
   <si>
     <t>Datum</t>
   </si>
@@ -57,16 +57,13 @@
     <t>proto-sequencer firmware</t>
   </si>
   <si>
-    <t>sequencer</t>
-  </si>
-  <si>
     <t>sequencer pcb</t>
   </si>
   <si>
-    <t>io unit schematic and pcb</t>
-  </si>
-  <si>
-    <t>frontpanel schematic and pcb</t>
+    <t>io unit pcb</t>
+  </si>
+  <si>
+    <t>frontpanel pcb</t>
   </si>
 </sst>
 </file>
@@ -439,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B2:D10"/>
+  <dimension ref="B2:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -506,32 +503,32 @@
         <v>45894</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
-        <v>45896</v>
+        <v>45894</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
-        <v>45897</v>
+        <v>45896</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.45">
@@ -539,10 +536,32 @@
         <v>45897</v>
       </c>
       <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B11" s="1">
+        <v>45897</v>
+      </c>
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="D10" t="s">
-        <v>9</v>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B12" s="1">
+        <v>45897</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6227DB57-67EF-4ABD-A492-F028E2482F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDEC567-84BD-4FB4-9F96-46447CA91D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
   <si>
     <t>Datum</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>frontpanel pcb</t>
+  </si>
+  <si>
+    <t>peripherals review and order</t>
   </si>
 </sst>
 </file>
@@ -436,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B2:D12"/>
+  <dimension ref="B2:D13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -562,6 +565,17 @@
       </c>
       <c r="D12" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B13" s="1">
+        <v>45898</v>
+      </c>
+      <c r="C13">
+        <v>0.5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDEC567-84BD-4FB4-9F96-46447CA91D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C46C7D-5E10-40EE-AC1F-605122AD680D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -48,9 +48,6 @@
     <t>Hora</t>
   </si>
   <si>
-    <t>21.08.2025</t>
-  </si>
-  <si>
     <t>USB Treiber 💀</t>
   </si>
   <si>
@@ -67,6 +64,9 @@
   </si>
   <si>
     <t>peripherals review and order</t>
+  </si>
+  <si>
+    <t>Bridge - Protokoll</t>
   </si>
 </sst>
 </file>
@@ -107,7 +107,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -439,14 +439,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B2:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:D13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C1">
+        <f>SUM(C3:C10000)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -457,18 +463,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B3" t="s">
-        <v>3</v>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="1">
+        <v>45890</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -476,10 +482,10 @@
         <v>0.5</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -487,10 +493,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -498,10 +504,10 @@
         <v>0.5</v>
       </c>
       <c r="D6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -509,10 +515,10 @@
         <v>0.5</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -520,10 +526,10 @@
         <v>0.5</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -531,10 +537,10 @@
         <v>1.5</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -542,10 +548,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -553,10 +559,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -564,10 +570,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -575,7 +581,7 @@
         <v>0.5</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -585,14 +591,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B2:D3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C1">
+        <f>SUM(C3:C10000)</f>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -603,15 +615,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B3" t="s">
-        <v>3</v>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="1">
+        <v>45890</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="1">
+        <v>45892</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="1">
+        <v>45898</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C46C7D-5E10-40EE-AC1F-605122AD680D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A43432-4724-4A51-989D-CE775EFA8BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
   <si>
     <t>Datum</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>Bridge - Protokoll</t>
+  </si>
+  <si>
+    <t>assembly mem unit</t>
+  </si>
+  <si>
+    <t>assembly ax08 lite</t>
   </si>
 </sst>
 </file>
@@ -107,7 +113,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -123,7 +129,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -439,20 +445,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:D13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -463,7 +469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -474,7 +480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -485,7 +491,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -496,7 +502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -507,7 +513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -518,7 +524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -529,7 +535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -540,7 +546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -551,7 +557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -562,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -573,7 +579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -582,6 +588,28 @@
       </c>
       <c r="D13" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B14" s="1">
+        <v>45901</v>
+      </c>
+      <c r="C14">
+        <v>1.5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B15" s="1">
+        <v>45901</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -592,19 +620,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
   <dimension ref="B1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>7.5</v>
       </c>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -615,7 +643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -626,7 +654,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -637,7 +665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45898</v>
       </c>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A43432-4724-4A51-989D-CE775EFA8BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EE8D8B-9E3D-44BC-A370-2F9638934634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
   <si>
     <t>Datum</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>assembly ax08 lite</t>
+  </si>
+  <si>
+    <t>first ax08 lite tests</t>
   </si>
 </sst>
 </file>
@@ -445,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:D15"/>
+  <dimension ref="B1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -455,7 +458,7 @@
     <row r="1" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
@@ -610,6 +613,17 @@
       </c>
       <c r="D15" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B16" s="1">
+        <v>45901</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EE8D8B-9E3D-44BC-A370-2F9638934634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD0F47D-0797-4535-AD53-AB1C0095C8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="14">
   <si>
     <t>Datum</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>first ax08 lite tests</t>
+  </si>
+  <si>
+    <t>preparing mem unit PICs</t>
   </si>
 </sst>
 </file>
@@ -448,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:D16"/>
+  <dimension ref="B1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -458,7 +461,7 @@
     <row r="1" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
@@ -624,6 +627,28 @@
       </c>
       <c r="D16" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B17" s="1">
+        <v>45902</v>
+      </c>
+      <c r="C17">
+        <v>1.5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B18" s="1">
+        <v>45902</v>
+      </c>
+      <c r="C18">
+        <v>1.5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD0F47D-0797-4535-AD53-AB1C0095C8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026A8B9B-C9DA-4B0F-867B-3B83D1971679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
   <si>
     <t>Datum</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>preparing mem unit PICs</t>
+  </si>
+  <si>
+    <t>architecture design discussion</t>
   </si>
 </sst>
 </file>
@@ -451,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:D18"/>
+  <dimension ref="B1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -461,7 +464,7 @@
     <row r="1" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>22.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
@@ -649,6 +652,17 @@
       </c>
       <c r="D18" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B19" s="1">
+        <v>45902</v>
+      </c>
+      <c r="C19">
+        <v>0.5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +672,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:D5"/>
+  <dimension ref="B1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11.3984375" customWidth="1"/>
@@ -668,7 +682,7 @@
     <row r="1" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
@@ -713,6 +727,17 @@
       </c>
       <c r="D5" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B6" s="1">
+        <v>45902</v>
+      </c>
+      <c r="C6">
+        <v>0.5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026A8B9B-C9DA-4B0F-867B-3B83D1971679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BC8AEE-107A-4C33-98BC-8B0E9487E56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="16">
   <si>
     <t>Datum</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>architecture design discussion</t>
+  </si>
+  <si>
+    <t>ax08 lite tests</t>
   </si>
 </sst>
 </file>
@@ -454,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:D19"/>
+  <dimension ref="B1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -464,7 +467,7 @@
     <row r="1" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
@@ -663,6 +666,17 @@
       </c>
       <c r="D19" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B20" s="1">
+        <v>45903</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -672,7 +686,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:D6"/>
+  <dimension ref="B1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11.3984375" customWidth="1"/>
@@ -682,7 +696,7 @@
     <row r="1" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
@@ -738,6 +752,17 @@
       </c>
       <c r="D6" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" s="1">
+        <v>45903</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BC8AEE-107A-4C33-98BC-8B0E9487E56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06225D6C-AA38-4FCE-8E3C-ED1B66D71B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t>Datum</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>ax08 lite tests</t>
+  </si>
+  <si>
+    <t>mem unit speedtests</t>
   </si>
 </sst>
 </file>
@@ -457,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:D20"/>
+  <dimension ref="B1:D22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -467,7 +470,7 @@
     <row r="1" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>27</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
@@ -676,6 +679,28 @@
         <v>4</v>
       </c>
       <c r="D20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B21" s="1">
+        <v>45904</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B22" s="1">
+        <v>45904</v>
+      </c>
+      <c r="C22">
+        <v>6.5</v>
+      </c>
+      <c r="D22" t="s">
         <v>15</v>
       </c>
     </row>
@@ -686,7 +711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:D7"/>
+  <dimension ref="B1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11.3984375" customWidth="1"/>
@@ -696,7 +721,7 @@
     <row r="1" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>12</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
@@ -762,6 +787,28 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B8" s="1">
+        <v>45904</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B9" s="1">
+        <v>45904</v>
+      </c>
+      <c r="C9">
+        <v>6.5</v>
+      </c>
+      <c r="D9" t="s">
         <v>15</v>
       </c>
     </row>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc project\rlpc\AX08-PC\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06225D6C-AA38-4FCE-8E3C-ED1B66D71B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66139D89-3F12-49F0-9FEE-BACBE4FFFC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
   <si>
     <t>Datum</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>mem unit speedtests</t>
+  </si>
+  <si>
+    <t>Sequencer Breadboard</t>
   </si>
 </sst>
 </file>
@@ -128,7 +131,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -144,7 +147,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -461,19 +464,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
   <dimension ref="B1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>36.5</v>
       </c>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -484,7 +487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -495,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -506,7 +509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -517,7 +520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -528,7 +531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -539,7 +542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -550,7 +553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -561,7 +564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -572,7 +575,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -583,7 +586,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -594,7 +597,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -605,7 +608,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -616,7 +619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -627,7 +630,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -638,7 +641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -649,7 +652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -660,7 +663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -671,7 +674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -682,7 +685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -693,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -711,20 +714,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:D10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -735,7 +738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -746,7 +749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -757,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -768,7 +771,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -779,7 +782,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -790,7 +793,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -801,7 +804,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -810,6 +813,17 @@
       </c>
       <c r="D9" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="1">
+        <v>45905</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66139D89-3F12-49F0-9FEE-BACBE4FFFC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74E8052-3336-4BB4-8DB5-AEFD1C69059E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t>Datum</t>
   </si>
@@ -91,6 +91,12 @@
   </si>
   <si>
     <t>Sequencer Breadboard</t>
+  </si>
+  <si>
+    <t>Optimize &amp; test memory unit, s2p and p2s modules</t>
+  </si>
+  <si>
+    <t>Rewrite sequencer</t>
   </si>
 </sst>
 </file>
@@ -714,7 +720,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:D10"/>
+  <dimension ref="B1:D12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -724,7 +730,7 @@
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>22.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
@@ -824,6 +830,28 @@
       </c>
       <c r="D10" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="1">
+        <v>45906</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
+        <v>45906</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74E8052-3336-4BB4-8DB5-AEFD1C69059E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD16F0D6-367B-477D-8980-0C535FEC565D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
   <si>
     <t>Datum</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>Rewrite sequencer</t>
+  </si>
+  <si>
+    <t>Testing mem unit firmware on pcb and fixing bugs</t>
   </si>
 </sst>
 </file>
@@ -720,7 +723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:D12"/>
+  <dimension ref="B1:D13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -730,7 +733,7 @@
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>30.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
@@ -852,6 +855,17 @@
       </c>
       <c r="D12" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="1">
+        <v>45907</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD16F0D6-367B-477D-8980-0C535FEC565D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C540EE7-77CF-4D95-BE3E-B5F87A66EF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
   <si>
     <t>Datum</t>
   </si>
@@ -100,6 +100,12 @@
   </si>
   <si>
     <t>Testing mem unit firmware on pcb and fixing bugs</t>
+  </si>
+  <si>
+    <t>Integration testing of the AX08L board</t>
+  </si>
+  <si>
+    <t>10kHz update</t>
   </si>
 </sst>
 </file>
@@ -472,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:D22"/>
+  <dimension ref="B1:D23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -482,7 +488,7 @@
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>36.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
@@ -714,6 +720,17 @@
       </c>
       <c r="D22" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="1">
+        <v>45907</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +740,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:D13"/>
+  <dimension ref="B1:D14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -733,7 +750,7 @@
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>31.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
@@ -866,6 +883,17 @@
       </c>
       <c r="D13" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="1">
+        <v>45907</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C540EE7-77CF-4D95-BE3E-B5F87A66EF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B01424E-5E17-4A20-8A0E-FDADB4102130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t>Datum</t>
   </si>
@@ -106,6 +106,24 @@
   </si>
   <si>
     <t>10kHz update</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Hardware</t>
+  </si>
+  <si>
+    <t>Firmware</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Optimize &amp; fix sequencer v1 firmware</t>
+  </si>
+  <si>
+    <t>Testing</t>
   </si>
 </sst>
 </file>
@@ -478,20 +496,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:D23"/>
+  <dimension ref="B1:E23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>37.5</v>
       </c>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -501,8 +520,11 @@
       <c r="D2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -512,8 +534,11 @@
       <c r="D3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -523,8 +548,11 @@
       <c r="D4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -534,8 +562,11 @@
       <c r="D5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -545,8 +576,11 @@
       <c r="D6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -556,8 +590,11 @@
       <c r="D7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -567,8 +604,11 @@
       <c r="D8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -578,8 +618,11 @@
       <c r="D9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -589,8 +632,11 @@
       <c r="D10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -600,8 +646,11 @@
       <c r="D11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -611,8 +660,11 @@
       <c r="D12" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -622,8 +674,11 @@
       <c r="D13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -633,8 +688,11 @@
       <c r="D14" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -644,8 +702,11 @@
       <c r="D15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -655,8 +716,11 @@
       <c r="D16" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -666,8 +730,11 @@
       <c r="D17" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -677,8 +744,11 @@
       <c r="D18" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -688,8 +758,11 @@
       <c r="D19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -699,8 +772,11 @@
       <c r="D20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -710,8 +786,11 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -721,8 +800,11 @@
       <c r="D22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -731,6 +813,9 @@
       </c>
       <c r="D23" t="s">
         <v>22</v>
+      </c>
+      <c r="E23" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -740,20 +825,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:D14"/>
+  <dimension ref="B1:E15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
     <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>32.5</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -763,8 +849,11 @@
       <c r="D2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -774,8 +863,11 @@
       <c r="D3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -785,8 +877,11 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -796,8 +891,11 @@
       <c r="D5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -807,8 +905,11 @@
       <c r="D6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -818,8 +919,11 @@
       <c r="D7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -829,8 +933,11 @@
       <c r="D8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -840,8 +947,11 @@
       <c r="D9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -851,8 +961,11 @@
       <c r="D10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -862,8 +975,11 @@
       <c r="D11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -873,8 +989,11 @@
       <c r="D12" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -884,8 +1003,11 @@
       <c r="D13" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -894,6 +1016,23 @@
       </c>
       <c r="D14" t="s">
         <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="1">
+        <v>45908</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B01424E-5E17-4A20-8A0E-FDADB4102130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680B0FF5-40E5-4C33-959E-AA6EA99C460D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="135" yWindow="780" windowWidth="21600" windowHeight="11835" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="31">
   <si>
     <t>Datum</t>
   </si>
@@ -124,6 +124,12 @@
   </si>
   <si>
     <t>Testing</t>
+  </si>
+  <si>
+    <t>Setup &amp; test breadboard io unit</t>
+  </si>
+  <si>
+    <t>sequencer speed testing</t>
   </si>
 </sst>
 </file>
@@ -496,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E23"/>
+  <dimension ref="B1:E24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -507,7 +513,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -815,6 +821,20 @@
         <v>22</v>
       </c>
       <c r="E23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="1">
+        <v>45909</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" t="s">
         <v>28</v>
       </c>
     </row>
@@ -825,7 +845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:E15"/>
+  <dimension ref="B1:E16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -836,7 +856,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>35.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -1033,6 +1053,20 @@
       </c>
       <c r="E15" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="1">
+        <v>45909</v>
+      </c>
+      <c r="C16">
+        <v>0.5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680B0FF5-40E5-4C33-959E-AA6EA99C460D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC5C3E4-9715-4CF9-AAB5-5350AB77D692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="780" windowWidth="21600" windowHeight="11835" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="39">
   <si>
     <t>Datum</t>
   </si>
@@ -87,9 +87,6 @@
     <t>ax08 lite tests</t>
   </si>
   <si>
-    <t>mem unit speedtests</t>
-  </si>
-  <si>
     <t>Sequencer Breadboard</t>
   </si>
   <si>
@@ -130,6 +127,33 @@
   </si>
   <si>
     <t>sequencer speed testing</t>
+  </si>
+  <si>
+    <t>assembly peripherals</t>
+  </si>
+  <si>
+    <t>memory testing</t>
+  </si>
+  <si>
+    <t>Tooling</t>
+  </si>
+  <si>
+    <t>Axiom toolkit 0.6</t>
+  </si>
+  <si>
+    <t>Memory testing</t>
+  </si>
+  <si>
+    <t>Mem unit speedtests</t>
+  </si>
+  <si>
+    <t>Peripherals review and order</t>
+  </si>
+  <si>
+    <t>Architecture design discussion</t>
+  </si>
+  <si>
+    <t>AX08 lite tests</t>
   </si>
 </sst>
 </file>
@@ -170,7 +194,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -186,7 +210,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -502,21 +526,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:E26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>38.5</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -527,10 +551,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -541,10 +565,10 @@
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -555,10 +579,10 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -569,10 +593,10 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -583,10 +607,10 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -597,10 +621,10 @@
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -611,10 +635,10 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -625,10 +649,10 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -639,10 +663,10 @@
         <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -653,10 +677,10 @@
         <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -667,10 +691,10 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -681,10 +705,10 @@
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -695,10 +719,10 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -709,10 +733,10 @@
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -723,10 +747,10 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -737,10 +761,10 @@
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -751,10 +775,10 @@
         <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -765,10 +789,10 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -779,10 +803,10 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -793,10 +817,10 @@
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -807,10 +831,10 @@
         <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -818,13 +842,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -832,10 +856,38 @@
         <v>1</v>
       </c>
       <c r="D24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B25" s="1">
+        <v>45910</v>
+      </c>
+      <c r="C25">
+        <v>1.5</v>
+      </c>
+      <c r="D25" t="s">
         <v>30</v>
       </c>
-      <c r="E24" t="s">
-        <v>28</v>
+      <c r="E25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B26" s="1">
+        <v>45910</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -845,21 +897,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:E16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:E18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -870,10 +922,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -884,10 +936,10 @@
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -898,10 +950,10 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -909,13 +961,13 @@
         <v>0.5</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -923,13 +975,13 @@
         <v>0.5</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -937,13 +989,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -951,13 +1003,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -965,13 +1017,13 @@
         <v>6.5</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -979,13 +1031,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -993,13 +1045,13 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1007,13 +1059,13 @@
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1021,13 +1073,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1035,13 +1087,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1049,13 +1101,13 @@
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1063,10 +1115,38 @@
         <v>0.5</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B17" s="1">
+        <v>45910</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B18" s="1">
+        <v>45910</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC5C3E4-9715-4CF9-AAB5-5350AB77D692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0835B1D-15D9-4630-8A33-1B57A3581CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="41">
   <si>
     <t>Datum</t>
   </si>
@@ -154,6 +154,12 @@
   </si>
   <si>
     <t>AX08 lite tests</t>
+  </si>
+  <si>
+    <t>ax08 main design</t>
+  </si>
+  <si>
+    <t>EDA</t>
   </si>
 </sst>
 </file>
@@ -526,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E26"/>
+  <dimension ref="B1:E28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -537,7 +543,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -635,7 +641,7 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
@@ -649,7 +655,7 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
@@ -663,7 +669,7 @@
         <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
@@ -677,7 +683,7 @@
         <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
@@ -705,7 +711,7 @@
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
@@ -789,7 +795,7 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
@@ -888,6 +894,34 @@
       </c>
       <c r="E26" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" s="1">
+        <v>45911</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B28" s="1">
+        <v>45911</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0835B1D-15D9-4630-8A33-1B57A3581CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81456EA5-4F33-4A29-A172-8D50E37DE8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="43">
   <si>
     <t>Datum</t>
   </si>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>EDA</t>
+  </si>
+  <si>
+    <t>Fix floating pins by using wpu / defining them as outputs</t>
+  </si>
+  <si>
+    <t>Increase internal bridge baud rate to 4Mbit</t>
   </si>
 </sst>
 </file>
@@ -200,7 +206,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -216,7 +222,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -533,20 +539,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
   <dimension ref="B1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -560,7 +566,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -574,7 +580,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -588,7 +594,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -602,7 +608,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -616,7 +622,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -630,7 +636,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -644,7 +650,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -658,7 +664,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -672,7 +678,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -686,7 +692,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -700,7 +706,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -714,7 +720,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -728,7 +734,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -742,7 +748,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -756,7 +762,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -770,7 +776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -784,7 +790,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -798,7 +804,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -812,7 +818,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -826,7 +832,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -840,7 +846,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -854,7 +860,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -868,7 +874,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -882,7 +888,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -896,7 +902,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -910,7 +916,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -931,21 +937,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:E18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:E20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -959,7 +965,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -973,7 +979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -987,7 +993,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1001,7 +1007,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1015,7 +1021,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1029,7 +1035,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1043,7 +1049,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1057,7 +1063,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1071,7 +1077,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1085,7 +1091,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1099,7 +1105,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1113,7 +1119,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1127,7 +1133,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1141,7 +1147,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1155,7 +1161,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1169,7 +1175,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1181,6 +1187,34 @@
       </c>
       <c r="E18" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="1">
+        <v>45911</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="1">
+        <v>45911</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81456EA5-4F33-4A29-A172-8D50E37DE8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841A3811-4FB8-4DCB-B2F9-459D7A4D9A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="43">
   <si>
     <t>Datum</t>
   </si>
@@ -206,7 +206,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -222,7 +222,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -538,21 +538,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:E29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -566,7 +566,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -580,7 +580,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -594,7 +594,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -608,7 +608,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -622,7 +622,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -636,7 +636,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -650,7 +650,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -664,7 +664,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -678,7 +678,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -692,7 +692,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -706,7 +706,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -720,7 +720,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -734,7 +734,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -748,7 +748,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -762,7 +762,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -776,7 +776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -790,7 +790,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -804,7 +804,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -818,7 +818,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -832,7 +832,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -846,7 +846,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -860,7 +860,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -874,7 +874,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -888,7 +888,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -902,7 +902,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -916,7 +916,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -927,6 +927,20 @@
         <v>39</v>
       </c>
       <c r="E28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B29" s="1">
+        <v>45912</v>
+      </c>
+      <c r="C29">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" t="s">
         <v>40</v>
       </c>
     </row>
@@ -938,20 +952,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
   <dimension ref="B1:E20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -965,7 +979,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -979,7 +993,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -993,7 +1007,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1007,7 +1021,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1021,7 +1035,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1035,7 +1049,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1049,7 +1063,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1063,7 +1077,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1077,7 +1091,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1091,7 +1105,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1105,7 +1119,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1119,7 +1133,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1133,7 +1147,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1147,7 +1161,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1161,7 +1175,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1175,7 +1189,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1189,7 +1203,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1203,7 +1217,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45911</v>
       </c>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841A3811-4FB8-4DCB-B2F9-459D7A4D9A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD61759E-540B-4CF8-9A11-D870727044DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="44">
   <si>
     <t>Datum</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>Increase internal bridge baud rate to 4Mbit</t>
+  </si>
+  <si>
+    <t>Program Upload /Chunks)</t>
   </si>
 </sst>
 </file>
@@ -206,7 +209,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -222,7 +225,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -539,20 +542,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
   <dimension ref="B1:E29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -566,7 +569,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -580,7 +583,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -594,7 +597,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -608,7 +611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -622,7 +625,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -636,7 +639,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -650,7 +653,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -664,7 +667,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -678,7 +681,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -692,7 +695,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -706,7 +709,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -720,7 +723,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -734,7 +737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -748,7 +751,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -762,7 +765,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -776,7 +779,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -790,7 +793,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -804,7 +807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -818,7 +821,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -832,7 +835,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -846,7 +849,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -860,7 +863,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -874,7 +877,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -888,7 +891,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -902,7 +905,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -916,7 +919,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -930,7 +933,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -951,21 +954,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:E20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:E23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -979,7 +982,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -993,7 +996,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1007,7 +1010,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1021,7 +1024,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1035,7 +1038,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1049,7 +1052,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1063,7 +1066,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1077,7 +1080,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1091,7 +1094,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1105,7 +1108,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1119,7 +1122,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1133,7 +1136,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1147,7 +1150,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1161,7 +1164,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1175,7 +1178,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1189,7 +1192,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1203,7 +1206,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1217,7 +1220,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1229,6 +1232,48 @@
       </c>
       <c r="E20" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="1">
+        <v>45912</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="1">
+        <v>45912</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="1">
+        <v>45912</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD61759E-540B-4CF8-9A11-D870727044DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4D1B3C-0BDE-42C7-BDA3-A388F43B9F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="45">
   <si>
     <t>Datum</t>
   </si>
@@ -169,6 +169,9 @@
   </si>
   <si>
     <t>Program Upload /Chunks)</t>
+  </si>
+  <si>
+    <t>ax08 main design (decode and logic unit)</t>
   </si>
 </sst>
 </file>
@@ -209,7 +212,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -225,7 +228,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -541,21 +544,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:E30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -569,7 +572,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -583,7 +586,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -597,7 +600,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -611,7 +614,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -625,7 +628,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -639,7 +642,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -653,7 +656,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -667,7 +670,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -681,7 +684,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -695,7 +698,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -709,7 +712,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -723,7 +726,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -737,7 +740,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -751,7 +754,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -765,7 +768,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -779,7 +782,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -793,7 +796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -807,7 +810,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -821,7 +824,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -835,7 +838,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -849,7 +852,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -863,7 +866,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -877,7 +880,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -891,7 +894,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -905,7 +908,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -919,7 +922,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -933,7 +936,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -944,6 +947,20 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B30" s="1">
+        <v>45915</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>40</v>
       </c>
     </row>
@@ -955,20 +972,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
   <dimension ref="B1:E23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -982,7 +999,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -996,7 +1013,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1010,7 +1027,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1024,7 +1041,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1038,7 +1055,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1052,7 +1069,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1066,7 +1083,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1080,7 +1097,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1094,7 +1111,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1108,7 +1125,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1122,7 +1139,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1136,7 +1153,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1150,7 +1167,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1164,7 +1181,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1178,7 +1195,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1192,7 +1209,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1206,7 +1223,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1220,7 +1237,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1234,7 +1251,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1248,7 +1265,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1262,7 +1279,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45912</v>
       </c>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4D1B3C-0BDE-42C7-BDA3-A388F43B9F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AAA5D6-7D1A-4C29-989E-56B9314A08C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="47">
   <si>
     <t>Datum</t>
   </si>
@@ -172,6 +172,12 @@
   </si>
   <si>
     <t>ax08 main design (decode and logic unit)</t>
+  </si>
+  <si>
+    <t>Start work on Axiom assembler v2 branch</t>
+  </si>
+  <si>
+    <t>Implement tokenizer</t>
   </si>
 </sst>
 </file>
@@ -212,7 +218,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -228,7 +234,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -545,20 +551,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
   <dimension ref="B1:E30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -572,7 +578,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -586,7 +592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -600,7 +606,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -614,7 +620,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -628,7 +634,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -642,7 +648,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -656,7 +662,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -670,7 +676,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -684,7 +690,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -698,7 +704,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -712,7 +718,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -726,7 +732,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -740,7 +746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -754,7 +760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -768,7 +774,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -782,7 +788,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -796,7 +802,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -810,7 +816,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -824,7 +830,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -838,7 +844,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -852,7 +858,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -866,7 +872,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -880,7 +886,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -894,7 +900,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -908,7 +914,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -922,7 +928,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -936,7 +942,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -950,7 +956,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -971,21 +977,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:E25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -999,7 +1005,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1013,7 +1019,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1027,7 +1033,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1041,7 +1047,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1055,7 +1061,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1069,7 +1075,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1083,7 +1089,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1097,7 +1103,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1111,7 +1117,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1125,7 +1131,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1139,7 +1145,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1153,7 +1159,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1167,7 +1173,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1181,7 +1187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1195,7 +1201,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1209,7 +1215,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1223,7 +1229,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1237,7 +1243,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1251,7 +1257,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1265,7 +1271,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1279,7 +1285,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1291,6 +1297,34 @@
       </c>
       <c r="E23" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="1">
+        <v>45548</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="1">
+        <v>45915</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AAA5D6-7D1A-4C29-989E-56B9314A08C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67B3EC7-0439-4A03-A17B-83FE8D38EA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
   <si>
     <t>Datum</t>
   </si>
@@ -218,7 +218,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -234,7 +234,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -550,21 +550,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:E31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -578,7 +578,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -592,7 +592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -606,7 +606,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -620,7 +620,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -634,7 +634,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -648,7 +648,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -662,7 +662,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -676,7 +676,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -690,7 +690,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -704,7 +704,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -718,7 +718,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -732,7 +732,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -746,7 +746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -760,7 +760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -774,7 +774,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -788,7 +788,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -802,7 +802,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -816,7 +816,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -830,7 +830,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -844,7 +844,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -858,7 +858,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -872,7 +872,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -886,7 +886,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -900,7 +900,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -914,7 +914,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -928,7 +928,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -942,7 +942,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -956,7 +956,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -967,6 +967,20 @@
         <v>44</v>
       </c>
       <c r="E30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B31" s="1">
+        <v>45916</v>
+      </c>
+      <c r="C31">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -978,20 +992,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
   <dimension ref="B1:E25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1005,7 +1019,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1019,7 +1033,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1033,7 +1047,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1047,7 +1061,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1061,7 +1075,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1075,7 +1089,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1089,7 +1103,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1103,7 +1117,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1117,7 +1131,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1131,7 +1145,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1145,7 +1159,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1159,7 +1173,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1173,7 +1187,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1187,7 +1201,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1201,7 +1215,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1215,7 +1229,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1229,7 +1243,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1243,7 +1257,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1257,7 +1271,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1271,7 +1285,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1285,7 +1299,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1299,7 +1313,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1313,7 +1327,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45915</v>
       </c>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67B3EC7-0439-4A03-A17B-83FE8D38EA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A946BBF6-C613-4256-BA9D-80BCC81225DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="48">
   <si>
     <t>Datum</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>Implement tokenizer</t>
+  </si>
+  <si>
+    <t>ax08 main design (decode, io, opcodes, carry)</t>
   </si>
 </sst>
 </file>
@@ -550,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E31"/>
+  <dimension ref="B1:E32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -561,7 +564,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>61</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -981,6 +984,20 @@
         <v>44</v>
       </c>
       <c r="E31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B32" s="1">
+        <v>45917</v>
+      </c>
+      <c r="C32">
+        <v>5.5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" t="s">
         <v>40</v>
       </c>
     </row>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A946BBF6-C613-4256-BA9D-80BCC81225DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973A93FE-E85D-4D5B-89ED-E74378749B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="49">
   <si>
     <t>Datum</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>ax08 main design (decode, io, opcodes, carry)</t>
+  </si>
+  <si>
+    <t>carry unit sanity check + documentation</t>
   </si>
 </sst>
 </file>
@@ -553,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E32"/>
+  <dimension ref="B1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -564,7 +567,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>66.5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -999,6 +1002,20 @@
       </c>
       <c r="E32" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B33" s="1">
+        <v>45917</v>
+      </c>
+      <c r="C33">
+        <v>0.5</v>
+      </c>
+      <c r="D33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973A93FE-E85D-4D5B-89ED-E74378749B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB09BC82-D7FA-41D6-B030-04DB167F141C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="52">
   <si>
     <t>Datum</t>
   </si>
@@ -184,6 +184,15 @@
   </si>
   <si>
     <t>carry unit sanity check + documentation</t>
+  </si>
+  <si>
+    <t>Finalize tokenizer of axasm v2</t>
+  </si>
+  <si>
+    <t>Implement token reader</t>
+  </si>
+  <si>
+    <t>axasm v2</t>
   </si>
 </sst>
 </file>
@@ -224,7 +233,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -240,7 +249,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -557,20 +566,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
   <dimension ref="B1:E33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -584,7 +593,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -598,7 +607,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -612,7 +621,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -626,7 +635,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -640,7 +649,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -654,7 +663,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -668,7 +677,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -682,7 +691,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -696,7 +705,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -710,7 +719,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -724,7 +733,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -738,7 +747,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -752,7 +761,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -766,7 +775,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -780,7 +789,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -794,7 +803,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -808,7 +817,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -822,7 +831,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -836,7 +845,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -850,7 +859,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -864,7 +873,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -878,7 +887,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -892,7 +901,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -906,7 +915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -920,7 +929,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -934,7 +943,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -948,7 +957,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -962,7 +971,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -976,7 +985,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -990,7 +999,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1004,7 +1013,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1025,21 +1034,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:E25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:F27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1053,7 +1062,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1067,7 +1076,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1081,7 +1090,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1095,7 +1104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1109,7 +1118,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1123,7 +1132,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1137,7 +1146,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1151,7 +1160,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1165,7 +1174,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1179,7 +1188,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1193,7 +1202,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1207,7 +1216,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1221,7 +1230,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1235,7 +1244,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1249,7 +1258,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1263,7 +1272,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1277,7 +1286,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1291,7 +1300,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1305,7 +1314,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1319,7 +1328,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1333,7 +1342,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1347,7 +1356,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1361,7 +1370,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1373,6 +1382,40 @@
       </c>
       <c r="E25" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="1">
+        <v>45916</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="1">
+        <v>45917</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB09BC82-D7FA-41D6-B030-04DB167F141C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B284B6A4-44A1-40DA-8D07-0F561BEB766F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="53">
   <si>
     <t>Datum</t>
   </si>
@@ -193,6 +193,9 @@
   </si>
   <si>
     <t>axasm v2</t>
+  </si>
+  <si>
+    <t>ax08 main design (carry unit, opcode logic)</t>
   </si>
 </sst>
 </file>
@@ -233,7 +236,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -249,7 +252,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -565,21 +568,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:E34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -593,7 +596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -607,7 +610,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -621,7 +624,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -635,7 +638,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -649,7 +652,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -663,7 +666,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -677,7 +680,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -691,7 +694,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -705,7 +708,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -719,7 +722,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -733,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -747,7 +750,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -761,7 +764,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -775,7 +778,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -789,7 +792,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -803,7 +806,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -817,7 +820,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -831,7 +834,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -845,7 +848,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -859,7 +862,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -873,7 +876,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -887,7 +890,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -901,7 +904,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -915,7 +918,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -929,7 +932,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -943,7 +946,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -957,7 +960,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -971,7 +974,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -985,7 +988,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -999,7 +1002,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1013,7 +1016,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1025,6 +1028,20 @@
       </c>
       <c r="E33" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B34" s="1">
+        <v>45918</v>
+      </c>
+      <c r="C34">
+        <v>7</v>
+      </c>
+      <c r="D34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1035,20 +1052,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
   <dimension ref="B1:F27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1062,7 +1079,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1076,7 +1093,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1090,7 +1107,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1104,7 +1121,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1118,7 +1135,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1132,7 +1149,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1146,7 +1163,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1160,7 +1177,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1174,7 +1191,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1188,7 +1205,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1202,7 +1219,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1216,7 +1233,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1230,7 +1247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1244,7 +1261,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1258,7 +1275,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1272,7 +1289,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1286,7 +1303,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1300,7 +1317,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1314,7 +1331,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1328,7 +1345,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1342,7 +1359,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1356,7 +1373,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1370,7 +1387,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1384,7 +1401,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45916</v>
       </c>
@@ -1401,7 +1418,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45917</v>
       </c>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B284B6A4-44A1-40DA-8D07-0F561BEB766F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D84C32-C662-4B13-B0FA-296E3BD4A112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="55">
   <si>
     <t>Datum</t>
   </si>
@@ -196,6 +196,12 @@
   </si>
   <si>
     <t>ax08 main design (carry unit, opcode logic)</t>
+  </si>
+  <si>
+    <t>ax08 main design (opcodes, cleanup)</t>
+  </si>
+  <si>
+    <t>ax08 main schematic review</t>
   </si>
 </sst>
 </file>
@@ -568,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E34"/>
+  <dimension ref="B1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -579,7 +585,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -1041,6 +1047,34 @@
         <v>52</v>
       </c>
       <c r="E34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B35" s="1">
+        <v>45918</v>
+      </c>
+      <c r="C35">
+        <v>1.5</v>
+      </c>
+      <c r="D35" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B36" s="1">
+        <v>45918</v>
+      </c>
+      <c r="C36">
+        <v>1.5</v>
+      </c>
+      <c r="D36" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" t="s">
         <v>40</v>
       </c>
     </row>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D84C32-C662-4B13-B0FA-296E3BD4A112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19399EBD-46AE-42F0-819C-BCBB82B5C305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="56">
   <si>
     <t>Datum</t>
   </si>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t>ax08 main schematic review</t>
+  </si>
+  <si>
+    <t>ax08 main finishing touch + review</t>
   </si>
 </sst>
 </file>
@@ -574,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E36"/>
+  <dimension ref="B1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -585,7 +588,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>77</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -1075,6 +1078,20 @@
         <v>54</v>
       </c>
       <c r="E36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B37" s="1">
+        <v>45919</v>
+      </c>
+      <c r="C37">
+        <v>0.5</v>
+      </c>
+      <c r="D37" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" t="s">
         <v>40</v>
       </c>
     </row>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19399EBD-46AE-42F0-819C-BCBB82B5C305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EF6643-93D5-41E0-9ACC-4E36AC773F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="57">
   <si>
     <t>Datum</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>ax08 main finishing touch + review</t>
+  </si>
+  <si>
+    <t>ax08 main review and order</t>
   </si>
 </sst>
 </file>
@@ -577,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E37"/>
+  <dimension ref="B1:E38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -588,7 +591,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>77.5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -1092,6 +1095,20 @@
         <v>55</v>
       </c>
       <c r="E37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B38" s="1">
+        <v>45921</v>
+      </c>
+      <c r="C38">
+        <v>0.5</v>
+      </c>
+      <c r="D38" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" t="s">
         <v>40</v>
       </c>
     </row>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EF6643-93D5-41E0-9ACC-4E36AC773F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED7D0C4-9609-423C-B1D6-B61AA0E2496B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="60">
   <si>
     <t>Datum</t>
   </si>
@@ -208,16 +208,31 @@
   </si>
   <si>
     <t>ax08 main review and order</t>
+  </si>
+  <si>
+    <t>Axiom Assembler v2 Design</t>
+  </si>
+  <si>
+    <t>Axiom Assembler v2 Implementation</t>
+  </si>
+  <si>
+    <t>Axiom Find Script</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -248,7 +263,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -264,7 +279,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -581,20 +596,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
   <dimension ref="B1:E38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -608,7 +623,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -622,7 +637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -636,7 +651,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -650,7 +665,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -664,7 +679,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -678,7 +693,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -692,7 +707,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -706,7 +721,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -720,7 +735,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -734,7 +749,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -748,7 +763,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -762,7 +777,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -776,7 +791,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -790,7 +805,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -804,7 +819,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -818,7 +833,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -832,7 +847,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -846,7 +861,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -860,7 +875,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -874,7 +889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -888,7 +903,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -902,7 +917,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -916,7 +931,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -930,7 +945,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -944,7 +959,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -958,7 +973,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -972,7 +987,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -986,7 +1001,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -1000,7 +1015,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -1014,7 +1029,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1028,7 +1043,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1042,7 +1057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>45918</v>
       </c>
@@ -1056,7 +1071,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>45918</v>
       </c>
@@ -1070,7 +1085,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>45918</v>
       </c>
@@ -1084,7 +1099,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>45919</v>
       </c>
@@ -1098,7 +1113,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>45921</v>
       </c>
@@ -1119,21 +1134,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:F32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1147,7 +1162,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1161,7 +1176,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1175,7 +1190,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1189,7 +1204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1203,7 +1218,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1217,7 +1232,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1231,7 +1246,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1245,7 +1260,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1259,7 +1274,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1273,7 +1288,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1287,7 +1302,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1301,7 +1316,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1315,7 +1330,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1329,7 +1344,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1343,7 +1358,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1357,7 +1372,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1371,7 +1386,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1385,7 +1400,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1399,7 +1414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1413,7 +1428,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1427,7 +1442,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1441,7 +1456,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1455,7 +1470,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1469,7 +1484,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45916</v>
       </c>
@@ -1486,7 +1501,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45917</v>
       </c>
@@ -1503,7 +1518,90 @@
         <v>51</v>
       </c>
     </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="1">
+        <v>45918</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="1">
+        <v>45919</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="1">
+        <v>45920</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="1">
+        <v>45921</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="1">
+        <v>45921</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED7D0C4-9609-423C-B1D6-B61AA0E2496B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE246BF5-D28B-4E1B-83F0-5EC676824B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="63">
   <si>
     <t>Datum</t>
   </si>
@@ -217,6 +217,15 @@
   </si>
   <si>
     <t>Axiom Find Script</t>
+  </si>
+  <si>
+    <t>Program Verification</t>
+  </si>
+  <si>
+    <t>FIrmware</t>
+  </si>
+  <si>
+    <t>Program Verify Debug</t>
   </si>
 </sst>
 </file>
@@ -595,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E38"/>
+  <dimension ref="B1:E39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -606,7 +615,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -1125,6 +1134,20 @@
       </c>
       <c r="E38" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="1">
+        <v>45922</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1134,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F32"/>
+  <dimension ref="B1:F34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -1145,7 +1168,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -1598,6 +1621,34 @@
       </c>
       <c r="E32" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="1">
+        <v>45922</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="1">
+        <v>45922</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE246BF5-D28B-4E1B-83F0-5EC676824B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108E8968-80CC-4E62-B001-A1E2B5A8668B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="68">
   <si>
     <t>Datum</t>
   </si>
@@ -225,7 +225,22 @@
     <t>FIrmware</t>
   </si>
   <si>
-    <t>Program Verify Debug</t>
+    <t>frontpanel v2 design</t>
+  </si>
+  <si>
+    <t>frontpanel v2 UI design</t>
+  </si>
+  <si>
+    <t>program verify debug</t>
+  </si>
+  <si>
+    <t>AX08 case concept design</t>
+  </si>
+  <si>
+    <t>AX08 case lid design</t>
+  </si>
+  <si>
+    <t>CAD</t>
   </si>
 </sst>
 </file>
@@ -272,7 +287,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -288,7 +303,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -604,21 +619,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:E41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -632,7 +647,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -646,7 +661,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -660,7 +675,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -674,7 +689,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -688,7 +703,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -702,7 +717,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -716,7 +731,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -730,7 +745,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -744,7 +759,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -758,7 +773,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -772,7 +787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -786,7 +801,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -800,7 +815,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -814,7 +829,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -828,7 +843,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -842,7 +857,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -856,7 +871,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -870,7 +885,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -884,7 +899,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -898,7 +913,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -912,7 +927,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -926,7 +941,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -940,7 +955,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -954,7 +969,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -968,7 +983,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -982,7 +997,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -996,7 +1011,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -1010,7 +1025,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -1024,7 +1039,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -1038,7 +1053,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1052,7 +1067,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1066,7 +1081,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" s="1">
         <v>45918</v>
       </c>
@@ -1080,7 +1095,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" s="1">
         <v>45918</v>
       </c>
@@ -1094,7 +1109,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" s="1">
         <v>45918</v>
       </c>
@@ -1108,7 +1123,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" s="1">
         <v>45919</v>
       </c>
@@ -1122,7 +1137,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" s="1">
         <v>45921</v>
       </c>
@@ -1136,7 +1151,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" s="1">
         <v>45922</v>
       </c>
@@ -1144,10 +1159,38 @@
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B40" s="1">
+        <v>45923</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B41" s="1">
+        <v>45923</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41" t="s">
+        <v>63</v>
+      </c>
+      <c r="E41" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1157,21 +1200,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:F36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1185,7 +1228,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1199,7 +1242,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1213,7 +1256,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1227,7 +1270,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1241,7 +1284,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1255,7 +1298,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1269,7 +1312,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1283,7 +1326,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1297,7 +1340,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1311,7 +1354,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1325,7 +1368,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1339,7 +1382,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1353,7 +1396,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1367,7 +1410,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1381,7 +1424,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1395,7 +1438,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1409,7 +1452,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1423,7 +1466,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1437,7 +1480,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1451,7 +1494,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1465,7 +1508,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1479,7 +1522,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1493,7 +1536,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1507,7 +1550,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45916</v>
       </c>
@@ -1524,7 +1567,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45917</v>
       </c>
@@ -1541,7 +1584,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45918</v>
       </c>
@@ -1558,7 +1601,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45919</v>
       </c>
@@ -1575,7 +1618,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>45920</v>
       </c>
@@ -1592,7 +1635,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B31" s="1">
         <v>45921</v>
       </c>
@@ -1609,7 +1652,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B32" s="1">
         <v>45921</v>
       </c>
@@ -1623,7 +1666,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" s="1">
         <v>45922</v>
       </c>
@@ -1637,7 +1680,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" s="1">
         <v>45922</v>
       </c>
@@ -1649,6 +1692,34 @@
       </c>
       <c r="E34" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B35" s="1">
+        <v>45923</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B36" s="1">
+        <v>45923</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>66</v>
+      </c>
+      <c r="E36" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108E8968-80CC-4E62-B001-A1E2B5A8668B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0509DAA8-15F5-4F91-9EE8-6A1CEB3541C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="71">
   <si>
     <t>Datum</t>
   </si>
@@ -241,6 +241,15 @@
   </si>
   <si>
     <t>CAD</t>
+  </si>
+  <si>
+    <t>Acquisition</t>
+  </si>
+  <si>
+    <t>frontpanel part list</t>
+  </si>
+  <si>
+    <t>AX08 case design</t>
   </si>
 </sst>
 </file>
@@ -619,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E41"/>
+  <dimension ref="B1:E43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -630,7 +639,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -1191,6 +1200,34 @@
       </c>
       <c r="E41" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B42" s="1">
+        <v>45924</v>
+      </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
+      <c r="D42" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B43" s="1">
+        <v>45924</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1200,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F36"/>
+  <dimension ref="B1:F38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11.3984375" customWidth="1"/>
@@ -1211,7 +1248,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -1719,6 +1756,34 @@
         <v>66</v>
       </c>
       <c r="E36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B37" s="1">
+        <v>45924</v>
+      </c>
+      <c r="C37">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B38" s="1">
+        <v>45924</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" t="s">
         <v>67</v>
       </c>
     </row>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0509DAA8-15F5-4F91-9EE8-6A1CEB3541C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16098604-B8FF-49F1-8BDF-0AC36142456C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="73">
   <si>
     <t>Datum</t>
   </si>
@@ -250,6 +250,12 @@
   </si>
   <si>
     <t>AX08 case design</t>
+  </si>
+  <si>
+    <t>frontpanel parts</t>
+  </si>
+  <si>
+    <t>consulting in the ax08 case design</t>
   </si>
 </sst>
 </file>
@@ -296,7 +302,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -312,7 +318,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -628,21 +634,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:E45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -656,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -670,7 +676,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -684,7 +690,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -698,7 +704,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -712,7 +718,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -726,7 +732,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -740,7 +746,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -754,7 +760,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -768,7 +774,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -782,7 +788,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -796,7 +802,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -810,7 +816,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -824,7 +830,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -838,7 +844,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -852,7 +858,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -866,7 +872,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -880,7 +886,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -894,7 +900,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -908,7 +914,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -922,7 +928,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -936,7 +942,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -950,7 +956,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -964,7 +970,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -978,7 +984,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -992,7 +998,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -1006,7 +1012,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -1020,7 +1026,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -1034,7 +1040,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -1048,7 +1054,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -1062,7 +1068,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1076,7 +1082,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1090,7 +1096,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>45918</v>
       </c>
@@ -1104,7 +1110,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>45918</v>
       </c>
@@ -1118,7 +1124,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>45918</v>
       </c>
@@ -1132,7 +1138,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>45919</v>
       </c>
@@ -1146,7 +1152,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>45921</v>
       </c>
@@ -1160,7 +1166,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
         <v>45922</v>
       </c>
@@ -1174,7 +1180,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
         <v>45923</v>
       </c>
@@ -1188,7 +1194,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
         <v>45923</v>
       </c>
@@ -1202,7 +1208,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
         <v>45924</v>
       </c>
@@ -1216,7 +1222,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
         <v>45924</v>
       </c>
@@ -1228,6 +1234,34 @@
       </c>
       <c r="E43" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B44" s="1">
+        <v>45925</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="s">
+        <v>71</v>
+      </c>
+      <c r="E44" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B45" s="1">
+        <v>45925</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1237,21 +1271,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:F40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1265,7 +1299,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1279,7 +1313,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1293,7 +1327,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1307,7 +1341,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1321,7 +1355,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1335,7 +1369,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1349,7 +1383,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1363,7 +1397,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1377,7 +1411,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1391,7 +1425,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1405,7 +1439,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1419,7 +1453,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1433,7 +1467,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1447,7 +1481,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1461,7 +1495,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1475,7 +1509,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1489,7 +1523,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1503,7 +1537,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1517,7 +1551,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1531,7 +1565,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1545,7 +1579,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1559,7 +1593,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1573,7 +1607,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1587,7 +1621,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45916</v>
       </c>
@@ -1604,7 +1638,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45917</v>
       </c>
@@ -1621,7 +1655,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45918</v>
       </c>
@@ -1638,7 +1672,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45919</v>
       </c>
@@ -1655,7 +1689,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45920</v>
       </c>
@@ -1672,7 +1706,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>45921</v>
       </c>
@@ -1689,7 +1723,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>45921</v>
       </c>
@@ -1703,7 +1737,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>45922</v>
       </c>
@@ -1717,7 +1751,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>45922</v>
       </c>
@@ -1731,7 +1765,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>45923</v>
       </c>
@@ -1745,7 +1779,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>45923</v>
       </c>
@@ -1759,7 +1793,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>45924</v>
       </c>
@@ -1773,7 +1807,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>45924</v>
       </c>
@@ -1784,6 +1818,34 @@
         <v>70</v>
       </c>
       <c r="E38" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="1">
+        <v>45925</v>
+      </c>
+      <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="1">
+        <v>45925</v>
+      </c>
+      <c r="C40">
+        <v>4</v>
+      </c>
+      <c r="D40" t="s">
+        <v>70</v>
+      </c>
+      <c r="E40" t="s">
         <v>67</v>
       </c>
     </row>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16098604-B8FF-49F1-8BDF-0AC36142456C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E69279-97E4-432F-B178-51404094E2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="79">
   <si>
     <t>Datum</t>
   </si>
@@ -256,6 +256,24 @@
   </si>
   <si>
     <t>consulting in the ax08 case design</t>
+  </si>
+  <si>
+    <t>AX08 case design frontpanel</t>
+  </si>
+  <si>
+    <t>ax08 case design frontpanel</t>
+  </si>
+  <si>
+    <t>Production of the case lid</t>
+  </si>
+  <si>
+    <t>Design of the case lid</t>
+  </si>
+  <si>
+    <t>design of the case lid</t>
+  </si>
+  <si>
+    <t>production of the case lid</t>
   </si>
 </sst>
 </file>
@@ -634,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E45"/>
+  <dimension ref="B1:E48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -645,7 +663,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -1262,6 +1280,48 @@
       </c>
       <c r="E45" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B46" s="1">
+        <v>46291</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" t="s">
+        <v>74</v>
+      </c>
+      <c r="E46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B47" s="1">
+        <v>46291</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47" t="s">
+        <v>77</v>
+      </c>
+      <c r="E47" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B48" s="1">
+        <v>46291</v>
+      </c>
+      <c r="C48">
+        <v>5</v>
+      </c>
+      <c r="D48" t="s">
+        <v>78</v>
+      </c>
+      <c r="E48" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1271,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F40"/>
+  <dimension ref="B1:F43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -1282,7 +1342,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -1847,6 +1907,48 @@
       </c>
       <c r="E40" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B41" s="1">
+        <v>46291</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B42" s="1">
+        <v>46291</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>76</v>
+      </c>
+      <c r="E42" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B43" s="1">
+        <v>46291</v>
+      </c>
+      <c r="C43">
+        <v>5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E69279-97E4-432F-B178-51404094E2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9BAA865-E966-4268-B294-8DBC52210071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="79">
   <si>
     <t>Datum</t>
   </si>
@@ -652,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E48"/>
+  <dimension ref="B1:E50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -663,7 +663,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -1321,6 +1321,34 @@
         <v>78</v>
       </c>
       <c r="E48" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="1">
+        <v>46292</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="D49" t="s">
+        <v>78</v>
+      </c>
+      <c r="E49" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="1">
+        <v>46292</v>
+      </c>
+      <c r="C50">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>78</v>
+      </c>
+      <c r="E50" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1331,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F43"/>
+  <dimension ref="B1:F45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -1342,7 +1370,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -1948,6 +1976,34 @@
         <v>75</v>
       </c>
       <c r="E43" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B44" s="1">
+        <v>46292</v>
+      </c>
+      <c r="C44">
+        <v>4</v>
+      </c>
+      <c r="D44" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B45" s="1">
+        <v>46292</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" t="s">
         <v>23</v>
       </c>
     </row>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9BAA865-E966-4268-B294-8DBC52210071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC4DAE7-3781-41E4-8107-60E96F88B503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="79">
   <si>
     <t>Datum</t>
   </si>
@@ -1359,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F45"/>
+  <dimension ref="B1:F46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -1370,7 +1370,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -2005,6 +2005,20 @@
       </c>
       <c r="E45" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B46" s="1">
+        <v>46293</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC4DAE7-3781-41E4-8107-60E96F88B503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A01EE9D-8E2C-4168-8AB1-AF7DFAB40924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="80">
   <si>
     <t>Datum</t>
   </si>
@@ -222,9 +222,6 @@
     <t>Program Verification</t>
   </si>
   <si>
-    <t>FIrmware</t>
-  </si>
-  <si>
     <t>frontpanel v2 design</t>
   </si>
   <si>
@@ -274,6 +271,12 @@
   </si>
   <si>
     <t>production of the case lid</t>
+  </si>
+  <si>
+    <t>EDA documentation file</t>
+  </si>
+  <si>
+    <t>Documentation</t>
   </si>
 </sst>
 </file>
@@ -320,7 +323,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -336,7 +339,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -652,21 +655,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:E51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -680,7 +683,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -694,7 +697,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -708,7 +711,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -722,7 +725,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -736,7 +739,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -750,7 +753,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -764,7 +767,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -778,7 +781,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -792,7 +795,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -806,7 +809,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -820,7 +823,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -834,7 +837,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -848,7 +851,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -862,7 +865,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -876,7 +879,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -890,7 +893,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -904,7 +907,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -918,7 +921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -932,7 +935,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -946,7 +949,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -960,7 +963,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -974,7 +977,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -988,7 +991,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -1002,7 +1005,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -1016,7 +1019,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -1030,7 +1033,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -1044,7 +1047,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -1058,7 +1061,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -1072,7 +1075,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -1086,7 +1089,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1100,7 +1103,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1114,7 +1117,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" s="1">
         <v>45918</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" s="1">
         <v>45918</v>
       </c>
@@ -1142,7 +1145,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" s="1">
         <v>45918</v>
       </c>
@@ -1156,7 +1159,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" s="1">
         <v>45919</v>
       </c>
@@ -1170,7 +1173,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" s="1">
         <v>45921</v>
       </c>
@@ -1184,7 +1187,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" s="1">
         <v>45922</v>
       </c>
@@ -1192,13 +1195,13 @@
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" s="1">
         <v>45923</v>
       </c>
@@ -1206,13 +1209,13 @@
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E40" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" s="1">
         <v>45923</v>
       </c>
@@ -1220,13 +1223,13 @@
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" s="1">
         <v>45924</v>
       </c>
@@ -1234,13 +1237,13 @@
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E42" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" s="1">
         <v>45924</v>
       </c>
@@ -1248,13 +1251,13 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E43" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" s="1">
         <v>45925</v>
       </c>
@@ -1262,13 +1265,13 @@
         <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E44" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" s="1">
         <v>45925</v>
       </c>
@@ -1276,13 +1279,13 @@
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E45" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" s="1">
         <v>46291</v>
       </c>
@@ -1290,13 +1293,13 @@
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" s="1">
         <v>46291</v>
       </c>
@@ -1304,13 +1307,13 @@
         <v>2</v>
       </c>
       <c r="D47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E47" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" s="1">
         <v>46291</v>
       </c>
@@ -1318,13 +1321,13 @@
         <v>5</v>
       </c>
       <c r="D48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E48" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B49" s="1">
         <v>46292</v>
       </c>
@@ -1332,13 +1335,13 @@
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E49" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" s="1">
         <v>46292</v>
       </c>
@@ -1346,10 +1349,24 @@
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E50" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B51" s="1">
+        <v>46299</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51" t="s">
+        <v>78</v>
+      </c>
+      <c r="E51" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1360,20 +1377,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
   <dimension ref="B1:F46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1387,7 +1404,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1401,7 +1418,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1415,7 +1432,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1429,7 +1446,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1443,7 +1460,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1457,7 +1474,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1471,7 +1488,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1485,7 +1502,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1499,7 +1516,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1513,7 +1530,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1527,7 +1544,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1541,7 +1558,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1555,7 +1572,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1569,7 +1586,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1583,7 +1600,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1597,7 +1614,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1611,7 +1628,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1625,7 +1642,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1639,7 +1656,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1653,7 +1670,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1667,7 +1684,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1681,7 +1698,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1695,7 +1712,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1709,7 +1726,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45916</v>
       </c>
@@ -1726,7 +1743,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45917</v>
       </c>
@@ -1743,7 +1760,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45918</v>
       </c>
@@ -1760,7 +1777,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45919</v>
       </c>
@@ -1777,7 +1794,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>45920</v>
       </c>
@@ -1794,7 +1811,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B31" s="1">
         <v>45921</v>
       </c>
@@ -1811,7 +1828,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B32" s="1">
         <v>45921</v>
       </c>
@@ -1825,7 +1842,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" s="1">
         <v>45922</v>
       </c>
@@ -1839,7 +1856,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" s="1">
         <v>45922</v>
       </c>
@@ -1850,10 +1867,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" s="1">
         <v>45923</v>
       </c>
@@ -1861,13 +1878,13 @@
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" s="1">
         <v>45923</v>
       </c>
@@ -1875,13 +1892,13 @@
         <v>4</v>
       </c>
       <c r="D36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" t="s">
         <v>66</v>
       </c>
-      <c r="E36" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" s="1">
         <v>45924</v>
       </c>
@@ -1889,13 +1906,13 @@
         <v>4</v>
       </c>
       <c r="D37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" t="s">
         <v>66</v>
       </c>
-      <c r="E37" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" s="1">
         <v>45924</v>
       </c>
@@ -1903,13 +1920,13 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" s="1">
         <v>45925</v>
       </c>
@@ -1917,13 +1934,13 @@
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" s="1">
         <v>45925</v>
       </c>
@@ -1931,13 +1948,13 @@
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" s="1">
         <v>46291</v>
       </c>
@@ -1945,13 +1962,13 @@
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" s="1">
         <v>46291</v>
       </c>
@@ -1959,13 +1976,13 @@
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E42" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" s="1">
         <v>46291</v>
       </c>
@@ -1973,13 +1990,13 @@
         <v>5</v>
       </c>
       <c r="D43" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E43" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" s="1">
         <v>46292</v>
       </c>
@@ -1987,13 +2004,13 @@
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E44" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" s="1">
         <v>46292</v>
       </c>
@@ -2001,13 +2018,13 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E45" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" s="1">
         <v>46293</v>
       </c>
@@ -2015,10 +2032,10 @@
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A01EE9D-8E2C-4168-8AB1-AF7DFAB40924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DECB5B4E-184D-4CCD-887A-094D19BF5E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="82">
   <si>
     <t>Datum</t>
   </si>
@@ -277,6 +277,12 @@
   </si>
   <si>
     <t>Documentation</t>
+  </si>
+  <si>
+    <t>Work on AXM v2</t>
+  </si>
+  <si>
+    <t>Case - AX08 Tray and Bracket</t>
   </si>
 </sst>
 </file>
@@ -323,7 +329,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -339,7 +345,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -656,20 +662,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
   <dimension ref="B1:E51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -683,7 +689,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -697,7 +703,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -711,7 +717,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -725,7 +731,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -739,7 +745,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -753,7 +759,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -767,7 +773,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -781,7 +787,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -795,7 +801,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -809,7 +815,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -823,7 +829,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -837,7 +843,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -851,7 +857,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -865,7 +871,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -879,7 +885,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -893,7 +899,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -907,7 +913,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -921,7 +927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -935,7 +941,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -949,7 +955,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -963,7 +969,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -977,7 +983,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -991,7 +997,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -1005,7 +1011,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -1019,7 +1025,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -1033,7 +1039,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -1047,7 +1053,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -1061,7 +1067,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -1075,7 +1081,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -1089,7 +1095,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1103,7 +1109,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1117,7 +1123,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>45918</v>
       </c>
@@ -1131,7 +1137,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>45918</v>
       </c>
@@ -1145,7 +1151,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>45918</v>
       </c>
@@ -1159,7 +1165,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>45919</v>
       </c>
@@ -1173,7 +1179,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>45921</v>
       </c>
@@ -1187,7 +1193,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
         <v>45922</v>
       </c>
@@ -1201,7 +1207,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
         <v>45923</v>
       </c>
@@ -1215,7 +1221,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
         <v>45923</v>
       </c>
@@ -1229,7 +1235,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
         <v>45924</v>
       </c>
@@ -1243,7 +1249,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
         <v>45924</v>
       </c>
@@ -1257,7 +1263,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="1">
         <v>45925</v>
       </c>
@@ -1271,7 +1277,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="1">
         <v>45925</v>
       </c>
@@ -1285,7 +1291,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="1">
         <v>46291</v>
       </c>
@@ -1299,7 +1305,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="1">
         <v>46291</v>
       </c>
@@ -1313,7 +1319,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="1">
         <v>46291</v>
       </c>
@@ -1327,7 +1333,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="1">
         <v>46292</v>
       </c>
@@ -1341,7 +1347,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="1">
         <v>46292</v>
       </c>
@@ -1355,7 +1361,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="1">
         <v>46299</v>
       </c>
@@ -1376,21 +1382,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:F48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1404,7 +1410,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1418,7 +1424,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1432,7 +1438,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1446,7 +1452,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1460,7 +1466,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1474,7 +1480,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1488,7 +1494,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1502,7 +1508,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1516,7 +1522,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1530,7 +1536,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1544,7 +1550,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1558,7 +1564,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1572,7 +1578,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1586,7 +1592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1600,7 +1606,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1614,7 +1620,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1628,7 +1634,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1642,7 +1648,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1656,7 +1662,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1670,7 +1676,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1684,7 +1690,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1698,7 +1704,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1712,7 +1718,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1726,7 +1732,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45916</v>
       </c>
@@ -1743,7 +1749,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45917</v>
       </c>
@@ -1760,7 +1766,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45918</v>
       </c>
@@ -1777,7 +1783,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45919</v>
       </c>
@@ -1794,7 +1800,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45920</v>
       </c>
@@ -1811,7 +1817,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>45921</v>
       </c>
@@ -1828,7 +1834,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>45921</v>
       </c>
@@ -1842,7 +1848,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>45922</v>
       </c>
@@ -1856,7 +1862,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>45922</v>
       </c>
@@ -1870,7 +1876,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>45923</v>
       </c>
@@ -1884,7 +1890,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>45923</v>
       </c>
@@ -1898,7 +1904,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>45924</v>
       </c>
@@ -1912,7 +1918,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>45924</v>
       </c>
@@ -1926,7 +1932,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
         <v>45925</v>
       </c>
@@ -1940,7 +1946,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
         <v>45925</v>
       </c>
@@ -1954,9 +1960,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
-        <v>46291</v>
+        <v>45926</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -1968,9 +1974,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
-        <v>46291</v>
+        <v>45926</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -1982,9 +1988,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
-        <v>46291</v>
+        <v>45926</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -1996,9 +2002,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="1">
-        <v>46292</v>
+        <v>45927</v>
       </c>
       <c r="C44">
         <v>4</v>
@@ -2010,9 +2016,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="1">
-        <v>46292</v>
+        <v>45927</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -2024,9 +2030,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="1">
-        <v>46293</v>
+        <v>45928</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2035,6 +2041,34 @@
         <v>69</v>
       </c>
       <c r="E46" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B47" s="1">
+        <v>45933</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B48" s="1">
+        <v>45934</v>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48" t="s">
+        <v>81</v>
+      </c>
+      <c r="E48" t="s">
         <v>66</v>
       </c>
     </row>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DECB5B4E-184D-4CCD-887A-094D19BF5E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D59567-4EC6-41FE-B3BB-E618D0BF510F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="83">
   <si>
     <t>Datum</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>Case - AX08 Tray and Bracket</t>
+  </si>
+  <si>
+    <t>Case - Cable Anchor</t>
   </si>
 </sst>
 </file>
@@ -329,7 +332,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -345,7 +348,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -661,21 +664,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:E52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="13.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -689,7 +692,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -703,7 +706,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -717,7 +720,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -731,7 +734,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -745,7 +748,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -759,7 +762,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -773,7 +776,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -787,7 +790,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -801,7 +804,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -815,7 +818,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -829,7 +832,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -843,7 +846,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -857,7 +860,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -871,7 +874,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -885,7 +888,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -899,7 +902,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -913,7 +916,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -927,7 +930,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -941,7 +944,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -955,7 +958,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -969,7 +972,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -983,7 +986,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -997,7 +1000,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -1011,7 +1014,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -1025,7 +1028,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -1039,7 +1042,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -1053,7 +1056,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -1067,7 +1070,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -1081,7 +1084,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -1095,7 +1098,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1109,7 +1112,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1123,7 +1126,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" s="1">
         <v>45918</v>
       </c>
@@ -1137,7 +1140,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" s="1">
         <v>45918</v>
       </c>
@@ -1151,7 +1154,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" s="1">
         <v>45918</v>
       </c>
@@ -1165,7 +1168,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" s="1">
         <v>45919</v>
       </c>
@@ -1179,7 +1182,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" s="1">
         <v>45921</v>
       </c>
@@ -1193,7 +1196,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" s="1">
         <v>45922</v>
       </c>
@@ -1207,7 +1210,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" s="1">
         <v>45923</v>
       </c>
@@ -1221,7 +1224,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" s="1">
         <v>45923</v>
       </c>
@@ -1235,7 +1238,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" s="1">
         <v>45924</v>
       </c>
@@ -1249,7 +1252,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" s="1">
         <v>45924</v>
       </c>
@@ -1263,7 +1266,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" s="1">
         <v>45925</v>
       </c>
@@ -1277,7 +1280,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" s="1">
         <v>45925</v>
       </c>
@@ -1291,7 +1294,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" s="1">
         <v>46291</v>
       </c>
@@ -1305,7 +1308,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" s="1">
         <v>46291</v>
       </c>
@@ -1319,7 +1322,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" s="1">
         <v>46291</v>
       </c>
@@ -1333,7 +1336,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B49" s="1">
         <v>46292</v>
       </c>
@@ -1347,7 +1350,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" s="1">
         <v>46292</v>
       </c>
@@ -1361,7 +1364,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" s="1">
         <v>46299</v>
       </c>
@@ -1372,6 +1375,20 @@
         <v>78</v>
       </c>
       <c r="E51" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B52" s="1">
+        <v>46300</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1382,21 +1399,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:F49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="13.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1410,7 +1427,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1424,7 +1441,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1438,7 +1455,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1452,7 +1469,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1466,7 +1483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1480,7 +1497,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1494,7 +1511,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1508,7 +1525,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1522,7 +1539,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1536,7 +1553,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1550,7 +1567,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1564,7 +1581,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1578,7 +1595,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1592,7 +1609,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1606,7 +1623,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1620,7 +1637,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1634,7 +1651,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1648,7 +1665,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1662,7 +1679,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1676,7 +1693,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1690,7 +1707,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1704,7 +1721,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1718,7 +1735,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1732,7 +1749,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45916</v>
       </c>
@@ -1749,7 +1766,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45917</v>
       </c>
@@ -1766,7 +1783,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45918</v>
       </c>
@@ -1783,7 +1800,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45919</v>
       </c>
@@ -1800,7 +1817,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>45920</v>
       </c>
@@ -1817,7 +1834,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B31" s="1">
         <v>45921</v>
       </c>
@@ -1834,7 +1851,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B32" s="1">
         <v>45921</v>
       </c>
@@ -1848,7 +1865,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" s="1">
         <v>45922</v>
       </c>
@@ -1862,7 +1879,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" s="1">
         <v>45922</v>
       </c>
@@ -1876,7 +1893,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" s="1">
         <v>45923</v>
       </c>
@@ -1890,7 +1907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" s="1">
         <v>45923</v>
       </c>
@@ -1904,7 +1921,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" s="1">
         <v>45924</v>
       </c>
@@ -1918,7 +1935,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" s="1">
         <v>45924</v>
       </c>
@@ -1932,7 +1949,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" s="1">
         <v>45925</v>
       </c>
@@ -1946,7 +1963,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" s="1">
         <v>45925</v>
       </c>
@@ -1960,7 +1977,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" s="1">
         <v>45926</v>
       </c>
@@ -1974,7 +1991,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" s="1">
         <v>45926</v>
       </c>
@@ -1988,7 +2005,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" s="1">
         <v>45926</v>
       </c>
@@ -2002,7 +2019,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" s="1">
         <v>45927</v>
       </c>
@@ -2016,7 +2033,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" s="1">
         <v>45927</v>
       </c>
@@ -2030,7 +2047,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" s="1">
         <v>45928</v>
       </c>
@@ -2044,7 +2061,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" s="1">
         <v>45933</v>
       </c>
@@ -2058,7 +2075,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" s="1">
         <v>45934</v>
       </c>
@@ -2069,6 +2086,20 @@
         <v>81</v>
       </c>
       <c r="E48" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B49" s="1">
+        <v>45935</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" t="s">
         <v>66</v>
       </c>
     </row>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D59567-4EC6-41FE-B3BB-E618D0BF510F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007459AA-68A8-47E6-8C17-03EE3EF93E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="84">
   <si>
     <t>Datum</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>Case - Cable Anchor</t>
+  </si>
+  <si>
+    <t>assembly ax08 main</t>
   </si>
 </sst>
 </file>
@@ -664,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E52"/>
+  <dimension ref="B1:E53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -675,7 +678,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -1390,6 +1393,20 @@
       </c>
       <c r="E52" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B53" s="1">
+        <v>46304</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53" t="s">
+        <v>83</v>
+      </c>
+      <c r="E53" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007459AA-68A8-47E6-8C17-03EE3EF93E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB286AF1-2606-4F94-A3EF-C2E0D3E4EF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="86">
   <si>
     <t>Datum</t>
   </si>
@@ -289,6 +289,12 @@
   </si>
   <si>
     <t>assembly ax08 main</t>
+  </si>
+  <si>
+    <t>assembly ax08</t>
+  </si>
+  <si>
+    <t>ax08 integration test</t>
   </si>
 </sst>
 </file>
@@ -667,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E53"/>
+  <dimension ref="B1:E55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -678,7 +684,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -1407,6 +1413,34 @@
       </c>
       <c r="E53" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B54" s="1">
+        <v>46308</v>
+      </c>
+      <c r="C54">
+        <v>9</v>
+      </c>
+      <c r="D54" t="s">
+        <v>84</v>
+      </c>
+      <c r="E54" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B55" s="1">
+        <v>46308</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="s">
+        <v>85</v>
+      </c>
+      <c r="E55" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB286AF1-2606-4F94-A3EF-C2E0D3E4EF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89D5922-76B5-4A1D-BE04-1EB899EEF61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="88">
   <si>
     <t>Datum</t>
   </si>
@@ -295,6 +295,12 @@
   </si>
   <si>
     <t>ax08 integration test</t>
+  </si>
+  <si>
+    <t>Design of the case lid glass cutting template</t>
+  </si>
+  <si>
+    <t>Cutting the case lid glass of case #2</t>
   </si>
 </sst>
 </file>
@@ -341,7 +347,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -357,7 +363,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -674,20 +680,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
   <dimension ref="B1:E55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="13.265625" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -701,7 +707,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -715,7 +721,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -729,7 +735,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -743,7 +749,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -757,7 +763,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -771,7 +777,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -785,7 +791,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -799,7 +805,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -813,7 +819,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -827,7 +833,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -841,7 +847,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -855,7 +861,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -869,7 +875,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -883,7 +889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -897,7 +903,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -911,7 +917,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -925,7 +931,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -939,7 +945,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -953,7 +959,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -967,7 +973,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -981,7 +987,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -995,7 +1001,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -1009,7 +1015,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -1023,7 +1029,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -1037,7 +1043,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -1051,7 +1057,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -1065,7 +1071,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -1079,7 +1085,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -1093,7 +1099,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -1107,7 +1113,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1121,7 +1127,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1135,7 +1141,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>45918</v>
       </c>
@@ -1149,7 +1155,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>45918</v>
       </c>
@@ -1163,7 +1169,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>45918</v>
       </c>
@@ -1177,7 +1183,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>45919</v>
       </c>
@@ -1191,7 +1197,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>45921</v>
       </c>
@@ -1205,7 +1211,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
         <v>45922</v>
       </c>
@@ -1219,7 +1225,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
         <v>45923</v>
       </c>
@@ -1233,7 +1239,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
         <v>45923</v>
       </c>
@@ -1247,7 +1253,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
         <v>45924</v>
       </c>
@@ -1261,7 +1267,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
         <v>45924</v>
       </c>
@@ -1275,7 +1281,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="1">
         <v>45925</v>
       </c>
@@ -1289,7 +1295,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="1">
         <v>45925</v>
       </c>
@@ -1303,7 +1309,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="1">
         <v>46291</v>
       </c>
@@ -1317,7 +1323,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="1">
         <v>46291</v>
       </c>
@@ -1331,7 +1337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="1">
         <v>46291</v>
       </c>
@@ -1345,7 +1351,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="1">
         <v>46292</v>
       </c>
@@ -1359,7 +1365,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="1">
         <v>46292</v>
       </c>
@@ -1373,7 +1379,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="1">
         <v>46299</v>
       </c>
@@ -1387,7 +1393,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="1">
         <v>46300</v>
       </c>
@@ -1401,7 +1407,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="1">
         <v>46304</v>
       </c>
@@ -1415,7 +1421,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="1">
         <v>46308</v>
       </c>
@@ -1429,7 +1435,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" s="1">
         <v>46308</v>
       </c>
@@ -1450,21 +1456,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:F51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="13.265625" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1478,7 +1484,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1492,7 +1498,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1506,7 +1512,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1520,7 +1526,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1534,7 +1540,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1548,7 +1554,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1562,7 +1568,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1576,7 +1582,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1590,7 +1596,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1604,7 +1610,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1618,7 +1624,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1632,7 +1638,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1646,7 +1652,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1660,7 +1666,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1674,7 +1680,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1688,7 +1694,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1702,7 +1708,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1716,7 +1722,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1730,7 +1736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1744,7 +1750,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1758,7 +1764,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1772,7 +1778,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1786,7 +1792,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1800,7 +1806,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45916</v>
       </c>
@@ -1817,7 +1823,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45917</v>
       </c>
@@ -1834,7 +1840,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45918</v>
       </c>
@@ -1851,7 +1857,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45919</v>
       </c>
@@ -1868,7 +1874,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45920</v>
       </c>
@@ -1885,7 +1891,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>45921</v>
       </c>
@@ -1902,7 +1908,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>45921</v>
       </c>
@@ -1916,7 +1922,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>45922</v>
       </c>
@@ -1930,7 +1936,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>45922</v>
       </c>
@@ -1944,7 +1950,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>45923</v>
       </c>
@@ -1958,7 +1964,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>45923</v>
       </c>
@@ -1972,7 +1978,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>45924</v>
       </c>
@@ -1986,7 +1992,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>45924</v>
       </c>
@@ -2000,7 +2006,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
         <v>45925</v>
       </c>
@@ -2014,7 +2020,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
         <v>45925</v>
       </c>
@@ -2028,7 +2034,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
         <v>45926</v>
       </c>
@@ -2042,7 +2048,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
         <v>45926</v>
       </c>
@@ -2056,7 +2062,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
         <v>45926</v>
       </c>
@@ -2070,7 +2076,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="1">
         <v>45927</v>
       </c>
@@ -2084,7 +2090,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="1">
         <v>45927</v>
       </c>
@@ -2098,7 +2104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="1">
         <v>45928</v>
       </c>
@@ -2112,7 +2118,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="1">
         <v>45933</v>
       </c>
@@ -2126,7 +2132,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="1">
         <v>45934</v>
       </c>
@@ -2140,7 +2146,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="1">
         <v>45935</v>
       </c>
@@ -2152,6 +2158,34 @@
       </c>
       <c r="E49" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C50">
+        <v>0.5</v>
+      </c>
+      <c r="D50" t="s">
+        <v>86</v>
+      </c>
+      <c r="E50" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C51">
+        <v>0.5</v>
+      </c>
+      <c r="D51" t="s">
+        <v>87</v>
+      </c>
+      <c r="E51" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89D5922-76B5-4A1D-BE04-1EB899EEF61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A3D976-F361-4DF2-89D1-8621D8408AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="89">
   <si>
     <t>Datum</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>Cutting the case lid glass of case #2</t>
+  </si>
+  <si>
+    <t>ax08 cables</t>
   </si>
 </sst>
 </file>
@@ -347,7 +350,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -363,7 +366,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -679,21 +682,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:E56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="13.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -707,7 +710,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -721,7 +724,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -735,7 +738,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -749,7 +752,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -763,7 +766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -777,7 +780,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -791,7 +794,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -805,7 +808,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -819,7 +822,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -833,7 +836,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -847,7 +850,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -861,7 +864,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -875,7 +878,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -889,7 +892,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -903,7 +906,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -917,7 +920,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -931,7 +934,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -945,7 +948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -959,7 +962,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -973,7 +976,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -987,7 +990,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -1001,7 +1004,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -1015,7 +1018,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -1029,7 +1032,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -1043,7 +1046,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -1057,7 +1060,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -1071,7 +1074,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -1085,7 +1088,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -1099,7 +1102,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -1113,7 +1116,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1127,7 +1130,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1141,7 +1144,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" s="1">
         <v>45918</v>
       </c>
@@ -1155,7 +1158,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" s="1">
         <v>45918</v>
       </c>
@@ -1169,7 +1172,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" s="1">
         <v>45918</v>
       </c>
@@ -1183,7 +1186,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" s="1">
         <v>45919</v>
       </c>
@@ -1197,7 +1200,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" s="1">
         <v>45921</v>
       </c>
@@ -1211,7 +1214,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" s="1">
         <v>45922</v>
       </c>
@@ -1225,7 +1228,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" s="1">
         <v>45923</v>
       </c>
@@ -1239,7 +1242,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" s="1">
         <v>45923</v>
       </c>
@@ -1253,7 +1256,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" s="1">
         <v>45924</v>
       </c>
@@ -1267,7 +1270,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" s="1">
         <v>45924</v>
       </c>
@@ -1281,7 +1284,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" s="1">
         <v>45925</v>
       </c>
@@ -1295,7 +1298,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" s="1">
         <v>45925</v>
       </c>
@@ -1309,7 +1312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" s="1">
         <v>46291</v>
       </c>
@@ -1323,7 +1326,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" s="1">
         <v>46291</v>
       </c>
@@ -1337,7 +1340,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" s="1">
         <v>46291</v>
       </c>
@@ -1351,7 +1354,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B49" s="1">
         <v>46292</v>
       </c>
@@ -1365,7 +1368,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" s="1">
         <v>46292</v>
       </c>
@@ -1379,7 +1382,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" s="1">
         <v>46299</v>
       </c>
@@ -1393,7 +1396,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B52" s="1">
         <v>46300</v>
       </c>
@@ -1407,7 +1410,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B53" s="1">
         <v>46304</v>
       </c>
@@ -1421,7 +1424,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B54" s="1">
         <v>46308</v>
       </c>
@@ -1435,7 +1438,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B55" s="1">
         <v>46308</v>
       </c>
@@ -1447,6 +1450,20 @@
       </c>
       <c r="E55" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B56" s="1">
+        <v>46309</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" t="s">
+        <v>88</v>
+      </c>
+      <c r="E56" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1457,20 +1474,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
   <dimension ref="B1:F51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="13.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1484,7 +1501,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1498,7 +1515,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1512,7 +1529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1526,7 +1543,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1540,7 +1557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1554,7 +1571,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1568,7 +1585,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1582,7 +1599,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1596,7 +1613,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1610,7 +1627,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1624,7 +1641,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1638,7 +1655,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1652,7 +1669,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1666,7 +1683,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1680,7 +1697,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1694,7 +1711,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1708,7 +1725,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1722,7 +1739,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1736,7 +1753,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1750,7 +1767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1764,7 +1781,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1778,7 +1795,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1792,7 +1809,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1806,7 +1823,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45916</v>
       </c>
@@ -1823,7 +1840,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45917</v>
       </c>
@@ -1840,7 +1857,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45918</v>
       </c>
@@ -1857,7 +1874,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45919</v>
       </c>
@@ -1874,7 +1891,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>45920</v>
       </c>
@@ -1891,7 +1908,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B31" s="1">
         <v>45921</v>
       </c>
@@ -1908,7 +1925,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B32" s="1">
         <v>45921</v>
       </c>
@@ -1922,7 +1939,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" s="1">
         <v>45922</v>
       </c>
@@ -1936,7 +1953,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" s="1">
         <v>45922</v>
       </c>
@@ -1950,7 +1967,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" s="1">
         <v>45923</v>
       </c>
@@ -1964,7 +1981,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" s="1">
         <v>45923</v>
       </c>
@@ -1978,7 +1995,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" s="1">
         <v>45924</v>
       </c>
@@ -1992,7 +2009,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" s="1">
         <v>45924</v>
       </c>
@@ -2006,7 +2023,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" s="1">
         <v>45925</v>
       </c>
@@ -2020,7 +2037,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" s="1">
         <v>45925</v>
       </c>
@@ -2034,7 +2051,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" s="1">
         <v>45926</v>
       </c>
@@ -2048,7 +2065,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" s="1">
         <v>45926</v>
       </c>
@@ -2062,7 +2079,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" s="1">
         <v>45926</v>
       </c>
@@ -2076,7 +2093,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" s="1">
         <v>45927</v>
       </c>
@@ -2090,7 +2107,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" s="1">
         <v>45927</v>
       </c>
@@ -2104,7 +2121,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" s="1">
         <v>45928</v>
       </c>
@@ -2118,7 +2135,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" s="1">
         <v>45933</v>
       </c>
@@ -2132,7 +2149,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" s="1">
         <v>45934</v>
       </c>
@@ -2146,7 +2163,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B49" s="1">
         <v>45935</v>
       </c>
@@ -2160,7 +2177,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" s="1">
         <v>45944</v>
       </c>
@@ -2174,7 +2191,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" s="1">
         <v>45944</v>
       </c>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A3D976-F361-4DF2-89D1-8621D8408AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC0C2FD-0CB6-4484-BF45-C3B924D5418A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
   <si>
     <t>Datum</t>
   </si>
@@ -304,6 +304,18 @@
   </si>
   <si>
     <t>ax08 cables</t>
+  </si>
+  <si>
+    <t>Measure current sequencer timings</t>
+  </si>
+  <si>
+    <t>Prototype sequencer update (unused)</t>
+  </si>
+  <si>
+    <t>Update existing sequencer v1 using lessons learned from v2</t>
+  </si>
+  <si>
+    <t>Add tx buffer to IO unit (+ some cleanup)</t>
   </si>
 </sst>
 </file>
@@ -350,7 +362,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -366,7 +378,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -683,20 +695,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
   <dimension ref="B1:E56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="13.265625" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -710,7 +722,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -724,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -738,7 +750,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -752,7 +764,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -766,7 +778,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -780,7 +792,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -794,7 +806,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -808,7 +820,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -822,7 +834,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -836,7 +848,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -850,7 +862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -864,7 +876,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -878,7 +890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -892,7 +904,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -906,7 +918,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -920,7 +932,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -934,7 +946,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -948,7 +960,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -962,7 +974,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -976,7 +988,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -990,7 +1002,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -1004,7 +1016,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -1018,7 +1030,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -1032,7 +1044,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -1046,7 +1058,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -1060,7 +1072,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -1074,7 +1086,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -1088,7 +1100,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -1102,7 +1114,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -1116,7 +1128,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1130,7 +1142,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1144,7 +1156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>45918</v>
       </c>
@@ -1158,7 +1170,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>45918</v>
       </c>
@@ -1172,7 +1184,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>45918</v>
       </c>
@@ -1186,7 +1198,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>45919</v>
       </c>
@@ -1200,7 +1212,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>45921</v>
       </c>
@@ -1214,7 +1226,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
         <v>45922</v>
       </c>
@@ -1228,7 +1240,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
         <v>45923</v>
       </c>
@@ -1242,7 +1254,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
         <v>45923</v>
       </c>
@@ -1256,7 +1268,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
         <v>45924</v>
       </c>
@@ -1270,7 +1282,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
         <v>45924</v>
       </c>
@@ -1284,7 +1296,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="1">
         <v>45925</v>
       </c>
@@ -1298,7 +1310,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="1">
         <v>45925</v>
       </c>
@@ -1312,7 +1324,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="1">
         <v>46291</v>
       </c>
@@ -1326,7 +1338,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="1">
         <v>46291</v>
       </c>
@@ -1340,7 +1352,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="1">
         <v>46291</v>
       </c>
@@ -1354,7 +1366,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="1">
         <v>46292</v>
       </c>
@@ -1368,7 +1380,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="1">
         <v>46292</v>
       </c>
@@ -1382,7 +1394,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="1">
         <v>46299</v>
       </c>
@@ -1396,7 +1408,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="1">
         <v>46300</v>
       </c>
@@ -1410,7 +1422,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="1">
         <v>46304</v>
       </c>
@@ -1424,7 +1436,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="1">
         <v>46308</v>
       </c>
@@ -1438,7 +1450,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" s="1">
         <v>46308</v>
       </c>
@@ -1452,7 +1464,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="1">
         <v>46309</v>
       </c>
@@ -1473,21 +1485,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:F55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="13.265625" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+        <v>113.5</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1501,7 +1513,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1515,7 +1527,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1529,7 +1541,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1543,7 +1555,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1557,7 +1569,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1571,7 +1583,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1585,7 +1597,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1599,7 +1611,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1613,7 +1625,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1627,7 +1639,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1641,7 +1653,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1655,7 +1667,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1669,7 +1681,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1683,7 +1695,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1697,7 +1709,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1711,7 +1723,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1725,7 +1737,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1739,7 +1751,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1753,7 +1765,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1767,7 +1779,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1781,7 +1793,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1795,7 +1807,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1809,7 +1821,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1823,7 +1835,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45916</v>
       </c>
@@ -1840,7 +1852,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45917</v>
       </c>
@@ -1857,7 +1869,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45918</v>
       </c>
@@ -1874,7 +1886,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45919</v>
       </c>
@@ -1891,7 +1903,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45920</v>
       </c>
@@ -1908,7 +1920,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>45921</v>
       </c>
@@ -1925,7 +1937,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>45921</v>
       </c>
@@ -1939,7 +1951,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>45922</v>
       </c>
@@ -1953,7 +1965,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>45922</v>
       </c>
@@ -1967,7 +1979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>45923</v>
       </c>
@@ -1981,7 +1993,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>45923</v>
       </c>
@@ -1995,7 +2007,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>45924</v>
       </c>
@@ -2009,7 +2021,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>45924</v>
       </c>
@@ -2023,7 +2035,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
         <v>45925</v>
       </c>
@@ -2037,7 +2049,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
         <v>45925</v>
       </c>
@@ -2051,7 +2063,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
         <v>45926</v>
       </c>
@@ -2065,7 +2077,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
         <v>45926</v>
       </c>
@@ -2079,7 +2091,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
         <v>45926</v>
       </c>
@@ -2093,7 +2105,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="1">
         <v>45927</v>
       </c>
@@ -2107,7 +2119,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="1">
         <v>45927</v>
       </c>
@@ -2121,7 +2133,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="1">
         <v>45928</v>
       </c>
@@ -2135,7 +2147,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="1">
         <v>45933</v>
       </c>
@@ -2149,7 +2161,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="1">
         <v>45934</v>
       </c>
@@ -2163,7 +2175,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="1">
         <v>45935</v>
       </c>
@@ -2177,7 +2189,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="1">
         <v>45944</v>
       </c>
@@ -2191,7 +2203,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="1">
         <v>45944</v>
       </c>
@@ -2203,6 +2215,62 @@
       </c>
       <c r="E51" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>92</v>
+      </c>
+      <c r="E52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
+        <v>89</v>
+      </c>
+      <c r="E53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>90</v>
+      </c>
+      <c r="E54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C55">
+        <v>0.5</v>
+      </c>
+      <c r="D55" t="s">
+        <v>91</v>
+      </c>
+      <c r="E55" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC0C2FD-0CB6-4484-BF45-C3B924D5418A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5918ABCE-E194-423E-B45C-A73AFA64D9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="96">
   <si>
     <t>Datum</t>
   </si>
@@ -316,6 +316,15 @@
   </si>
   <si>
     <t>Add tx buffer to IO unit (+ some cleanup)</t>
+  </si>
+  <si>
+    <t>io unit testing</t>
+  </si>
+  <si>
+    <t>IO unit testing</t>
+  </si>
+  <si>
+    <t>IO unit TX buffer</t>
   </si>
 </sst>
 </file>
@@ -362,7 +371,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -378,7 +387,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -694,21 +703,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:E58"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="13.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -722,7 +731,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -736,7 +745,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -750,7 +759,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -764,7 +773,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -778,7 +787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -792,7 +801,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -806,7 +815,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -820,7 +829,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -834,7 +843,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -848,7 +857,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -862,7 +871,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -876,7 +885,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -890,7 +899,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -904,7 +913,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -918,7 +927,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -932,7 +941,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -946,7 +955,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -960,7 +969,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -974,7 +983,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -988,7 +997,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -1002,7 +1011,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -1016,7 +1025,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -1030,7 +1039,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -1044,7 +1053,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -1058,7 +1067,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -1072,7 +1081,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -1086,7 +1095,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -1100,7 +1109,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -1114,7 +1123,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -1128,7 +1137,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1142,7 +1151,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1156,7 +1165,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" s="1">
         <v>45918</v>
       </c>
@@ -1170,7 +1179,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" s="1">
         <v>45918</v>
       </c>
@@ -1184,7 +1193,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" s="1">
         <v>45918</v>
       </c>
@@ -1198,7 +1207,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" s="1">
         <v>45919</v>
       </c>
@@ -1212,7 +1221,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" s="1">
         <v>45921</v>
       </c>
@@ -1226,7 +1235,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" s="1">
         <v>45922</v>
       </c>
@@ -1240,7 +1249,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" s="1">
         <v>45923</v>
       </c>
@@ -1254,7 +1263,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" s="1">
         <v>45923</v>
       </c>
@@ -1268,7 +1277,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" s="1">
         <v>45924</v>
       </c>
@@ -1282,7 +1291,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" s="1">
         <v>45924</v>
       </c>
@@ -1296,7 +1305,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" s="1">
         <v>45925</v>
       </c>
@@ -1310,7 +1319,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" s="1">
         <v>45925</v>
       </c>
@@ -1324,7 +1333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" s="1">
         <v>46291</v>
       </c>
@@ -1338,7 +1347,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" s="1">
         <v>46291</v>
       </c>
@@ -1352,7 +1361,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" s="1">
         <v>46291</v>
       </c>
@@ -1366,7 +1375,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B49" s="1">
         <v>46292</v>
       </c>
@@ -1380,7 +1389,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" s="1">
         <v>46292</v>
       </c>
@@ -1394,7 +1403,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" s="1">
         <v>46299</v>
       </c>
@@ -1408,7 +1417,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B52" s="1">
         <v>46300</v>
       </c>
@@ -1422,7 +1431,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B53" s="1">
         <v>46304</v>
       </c>
@@ -1436,7 +1445,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B54" s="1">
         <v>46308</v>
       </c>
@@ -1450,7 +1459,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B55" s="1">
         <v>46308</v>
       </c>
@@ -1464,7 +1473,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" s="1">
         <v>46309</v>
       </c>
@@ -1476,6 +1485,34 @@
       </c>
       <c r="E56" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B57" s="1">
+        <v>46310</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>88</v>
+      </c>
+      <c r="E57" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B58" s="1">
+        <v>46310</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
+        <v>93</v>
+      </c>
+      <c r="E58" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1485,21 +1522,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:F57"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="52.73046875" customWidth="1"/>
+    <col min="5" max="5" width="13.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>113.5</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>115.5</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1513,7 +1550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1527,7 +1564,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1541,7 +1578,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1555,7 +1592,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1569,7 +1606,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1583,7 +1620,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1597,7 +1634,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1611,7 +1648,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1625,7 +1662,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1639,7 +1676,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1653,7 +1690,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1667,7 +1704,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1681,7 +1718,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1695,7 +1732,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1709,7 +1746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1723,7 +1760,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1737,7 +1774,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1751,7 +1788,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1765,7 +1802,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1779,7 +1816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1793,7 +1830,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1807,7 +1844,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1821,7 +1858,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1835,7 +1872,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>45916</v>
       </c>
@@ -1852,7 +1889,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>45917</v>
       </c>
@@ -1869,7 +1906,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>45918</v>
       </c>
@@ -1886,7 +1923,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>45919</v>
       </c>
@@ -1903,7 +1940,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>45920</v>
       </c>
@@ -1920,7 +1957,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B31" s="1">
         <v>45921</v>
       </c>
@@ -1937,7 +1974,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B32" s="1">
         <v>45921</v>
       </c>
@@ -1951,7 +1988,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" s="1">
         <v>45922</v>
       </c>
@@ -1965,7 +2002,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" s="1">
         <v>45922</v>
       </c>
@@ -1979,7 +2016,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" s="1">
         <v>45923</v>
       </c>
@@ -1993,7 +2030,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" s="1">
         <v>45923</v>
       </c>
@@ -2007,7 +2044,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" s="1">
         <v>45924</v>
       </c>
@@ -2021,7 +2058,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" s="1">
         <v>45924</v>
       </c>
@@ -2035,7 +2072,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" s="1">
         <v>45925</v>
       </c>
@@ -2049,7 +2086,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" s="1">
         <v>45925</v>
       </c>
@@ -2063,7 +2100,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" s="1">
         <v>45926</v>
       </c>
@@ -2077,7 +2114,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" s="1">
         <v>45926</v>
       </c>
@@ -2091,7 +2128,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" s="1">
         <v>45926</v>
       </c>
@@ -2105,7 +2142,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" s="1">
         <v>45927</v>
       </c>
@@ -2119,7 +2156,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" s="1">
         <v>45927</v>
       </c>
@@ -2133,7 +2170,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" s="1">
         <v>45928</v>
       </c>
@@ -2147,7 +2184,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" s="1">
         <v>45933</v>
       </c>
@@ -2161,7 +2198,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" s="1">
         <v>45934</v>
       </c>
@@ -2175,7 +2212,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B49" s="1">
         <v>45935</v>
       </c>
@@ -2189,7 +2226,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" s="1">
         <v>45944</v>
       </c>
@@ -2203,7 +2240,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" s="1">
         <v>45944</v>
       </c>
@@ -2217,7 +2254,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B52" s="1">
         <v>45944</v>
       </c>
@@ -2231,7 +2268,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B53" s="1">
         <v>45945</v>
       </c>
@@ -2245,7 +2282,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B54" s="1">
         <v>45945</v>
       </c>
@@ -2259,7 +2296,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B55" s="1">
         <v>45945</v>
       </c>
@@ -2271,6 +2308,34 @@
       </c>
       <c r="E55" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B56" s="1">
+        <v>46310</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B57" s="1">
+        <v>46310</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>94</v>
+      </c>
+      <c r="E57" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5918ABCE-E194-423E-B45C-A73AFA64D9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6797832E-185B-49D9-985D-1111D14F7FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="97">
   <si>
     <t>Datum</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>IO unit TX buffer</t>
+  </si>
+  <si>
+    <t>assembly ax08 peripherals</t>
   </si>
 </sst>
 </file>
@@ -703,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E58"/>
+  <dimension ref="B1:E59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -714,7 +717,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>131</v>
+        <v>133.5</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -1489,7 +1492,7 @@
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -1503,7 +1506,7 @@
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -1513,6 +1516,20 @@
       </c>
       <c r="E58" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B59" s="1">
+        <v>46312</v>
+      </c>
+      <c r="C59">
+        <v>2.5</v>
+      </c>
+      <c r="D59" t="s">
+        <v>96</v>
+      </c>
+      <c r="E59" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2312,7 +2329,7 @@
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -2326,7 +2343,7 @@
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C57">
         <v>1</v>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6797832E-185B-49D9-985D-1111D14F7FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB7C105-0633-4253-9A9C-0394BE15C139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="97">
   <si>
     <t>Datum</t>
   </si>
@@ -706,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E59"/>
+  <dimension ref="B1:E60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -717,7 +717,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>133.5</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -1529,6 +1529,20 @@
         <v>96</v>
       </c>
       <c r="E59" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B60" s="1">
+        <v>46312</v>
+      </c>
+      <c r="C60">
+        <v>1.5</v>
+      </c>
+      <c r="D60" t="s">
+        <v>88</v>
+      </c>
+      <c r="E60" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1539,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F57"/>
+  <dimension ref="B1:F58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11.3984375" customWidth="1"/>
@@ -1550,7 +1564,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>115.5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -2352,6 +2366,20 @@
         <v>94</v>
       </c>
       <c r="E57" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B58" s="1">
+        <v>46312</v>
+      </c>
+      <c r="C58">
+        <v>1.5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>94</v>
+      </c>
+      <c r="E58" t="s">
         <v>27</v>
       </c>
     </row>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olive\Desktop\pc_project\rlpc\AX08-PC\project_mismanagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB7C105-0633-4253-9A9C-0394BE15C139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE265627-68EA-4A96-B948-1D258018FD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="100">
   <si>
     <t>Datum</t>
   </si>
@@ -328,6 +328,15 @@
   </si>
   <si>
     <t>assembly ax08 peripherals</t>
+  </si>
+  <si>
+    <t>Small changes to case (feedback of case #1)</t>
+  </si>
+  <si>
+    <t>Manufacturing of case #2</t>
+  </si>
+  <si>
+    <t>Finish IO unit TX buffer (and check the TXIE bit 💀)</t>
   </si>
 </sst>
 </file>
@@ -374,7 +383,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -390,7 +399,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -707,20 +716,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
   <dimension ref="B1:E60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="13.265625" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -734,7 +743,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -748,7 +757,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45891</v>
       </c>
@@ -762,7 +771,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45892</v>
       </c>
@@ -776,7 +785,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45893</v>
       </c>
@@ -790,7 +799,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45894</v>
       </c>
@@ -804,7 +813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45894</v>
       </c>
@@ -818,7 +827,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45896</v>
       </c>
@@ -832,7 +841,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45897</v>
       </c>
@@ -846,7 +855,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45897</v>
       </c>
@@ -860,7 +869,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45897</v>
       </c>
@@ -874,7 +883,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45898</v>
       </c>
@@ -888,7 +897,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45901</v>
       </c>
@@ -902,7 +911,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45901</v>
       </c>
@@ -916,7 +925,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45901</v>
       </c>
@@ -930,7 +939,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45902</v>
       </c>
@@ -944,7 +953,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45902</v>
       </c>
@@ -958,7 +967,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45902</v>
       </c>
@@ -972,7 +981,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45903</v>
       </c>
@@ -986,7 +995,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45904</v>
       </c>
@@ -1000,7 +1009,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45904</v>
       </c>
@@ -1014,7 +1023,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45907</v>
       </c>
@@ -1028,7 +1037,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45909</v>
       </c>
@@ -1042,7 +1051,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45910</v>
       </c>
@@ -1056,7 +1065,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45910</v>
       </c>
@@ -1070,7 +1079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45911</v>
       </c>
@@ -1084,7 +1093,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45911</v>
       </c>
@@ -1098,7 +1107,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45912</v>
       </c>
@@ -1112,7 +1121,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45915</v>
       </c>
@@ -1126,7 +1135,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>45916</v>
       </c>
@@ -1140,7 +1149,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>45917</v>
       </c>
@@ -1154,7 +1163,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>45917</v>
       </c>
@@ -1168,7 +1177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>45918</v>
       </c>
@@ -1182,7 +1191,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>45918</v>
       </c>
@@ -1196,7 +1205,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>45918</v>
       </c>
@@ -1210,7 +1219,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>45919</v>
       </c>
@@ -1224,7 +1233,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>45921</v>
       </c>
@@ -1238,7 +1247,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
         <v>45922</v>
       </c>
@@ -1252,7 +1261,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
         <v>45923</v>
       </c>
@@ -1266,7 +1275,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
         <v>45923</v>
       </c>
@@ -1280,7 +1289,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
         <v>45924</v>
       </c>
@@ -1294,7 +1303,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
         <v>45924</v>
       </c>
@@ -1308,7 +1317,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="1">
         <v>45925</v>
       </c>
@@ -1322,7 +1331,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="1">
         <v>45925</v>
       </c>
@@ -1336,7 +1345,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="1">
         <v>46291</v>
       </c>
@@ -1350,7 +1359,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="1">
         <v>46291</v>
       </c>
@@ -1364,7 +1373,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="1">
         <v>46291</v>
       </c>
@@ -1378,7 +1387,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="1">
         <v>46292</v>
       </c>
@@ -1392,7 +1401,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="1">
         <v>46292</v>
       </c>
@@ -1406,7 +1415,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="1">
         <v>46299</v>
       </c>
@@ -1420,7 +1429,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="1">
         <v>46300</v>
       </c>
@@ -1434,7 +1443,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="1">
         <v>46304</v>
       </c>
@@ -1448,7 +1457,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="1">
         <v>46308</v>
       </c>
@@ -1462,7 +1471,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" s="1">
         <v>46308</v>
       </c>
@@ -1476,7 +1485,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="1">
         <v>46309</v>
       </c>
@@ -1490,7 +1499,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" s="1">
         <v>46311</v>
       </c>
@@ -1504,7 +1513,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="1">
         <v>46311</v>
       </c>
@@ -1518,7 +1527,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" s="1">
         <v>46312</v>
       </c>
@@ -1532,7 +1541,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60" s="1">
         <v>46312</v>
       </c>
@@ -1553,21 +1562,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:F61"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="4" max="4" width="52.73046875" customWidth="1"/>
-    <col min="5" max="5" width="13.265625" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1581,7 +1590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>45890</v>
       </c>
@@ -1595,7 +1604,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>45892</v>
       </c>
@@ -1609,7 +1618,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>45898</v>
       </c>
@@ -1623,7 +1632,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>45902</v>
       </c>
@@ -1637,7 +1646,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>45903</v>
       </c>
@@ -1651,7 +1660,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>45904</v>
       </c>
@@ -1665,7 +1674,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>45904</v>
       </c>
@@ -1679,7 +1688,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>45905</v>
       </c>
@@ -1693,7 +1702,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>45906</v>
       </c>
@@ -1707,7 +1716,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>45906</v>
       </c>
@@ -1721,7 +1730,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>45907</v>
       </c>
@@ -1735,7 +1744,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>45907</v>
       </c>
@@ -1749,7 +1758,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>45908</v>
       </c>
@@ -1763,7 +1772,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>45909</v>
       </c>
@@ -1777,7 +1786,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>45910</v>
       </c>
@@ -1791,7 +1800,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>45910</v>
       </c>
@@ -1805,7 +1814,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>45911</v>
       </c>
@@ -1819,7 +1828,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>45911</v>
       </c>
@@ -1833,7 +1842,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>45912</v>
       </c>
@@ -1847,7 +1856,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>45912</v>
       </c>
@@ -1861,7 +1870,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>45912</v>
       </c>
@@ -1875,7 +1884,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>45548</v>
       </c>
@@ -1889,7 +1898,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>45915</v>
       </c>
@@ -1903,7 +1912,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>45916</v>
       </c>
@@ -1920,7 +1929,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>45917</v>
       </c>
@@ -1937,7 +1946,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>45918</v>
       </c>
@@ -1954,7 +1963,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45919</v>
       </c>
@@ -1971,7 +1980,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>45920</v>
       </c>
@@ -1988,7 +1997,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>45921</v>
       </c>
@@ -2005,7 +2014,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>45921</v>
       </c>
@@ -2019,7 +2028,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>45922</v>
       </c>
@@ -2033,7 +2042,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>45922</v>
       </c>
@@ -2047,7 +2056,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>45923</v>
       </c>
@@ -2061,7 +2070,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>45923</v>
       </c>
@@ -2075,7 +2084,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>45924</v>
       </c>
@@ -2089,7 +2098,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>45924</v>
       </c>
@@ -2103,7 +2112,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
         <v>45925</v>
       </c>
@@ -2117,7 +2126,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
         <v>45925</v>
       </c>
@@ -2131,7 +2140,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
         <v>45926</v>
       </c>
@@ -2145,7 +2154,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
         <v>45926</v>
       </c>
@@ -2159,7 +2168,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
         <v>45926</v>
       </c>
@@ -2173,7 +2182,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="1">
         <v>45927</v>
       </c>
@@ -2187,7 +2196,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="1">
         <v>45927</v>
       </c>
@@ -2201,7 +2210,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="1">
         <v>45928</v>
       </c>
@@ -2215,7 +2224,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="1">
         <v>45933</v>
       </c>
@@ -2229,7 +2238,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="1">
         <v>45934</v>
       </c>
@@ -2243,7 +2252,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="1">
         <v>45935</v>
       </c>
@@ -2257,7 +2266,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="1">
         <v>45944</v>
       </c>
@@ -2271,7 +2280,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="1">
         <v>45944</v>
       </c>
@@ -2285,7 +2294,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="1">
         <v>45944</v>
       </c>
@@ -2299,7 +2308,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="1">
         <v>45945</v>
       </c>
@@ -2313,7 +2322,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="1">
         <v>45945</v>
       </c>
@@ -2327,7 +2336,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" s="1">
         <v>45945</v>
       </c>
@@ -2341,7 +2350,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="1">
         <v>46311</v>
       </c>
@@ -2355,7 +2364,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" s="1">
         <v>46311</v>
       </c>
@@ -2369,7 +2378,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="1">
         <v>46312</v>
       </c>
@@ -2381,6 +2390,45 @@
       </c>
       <c r="E58" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="1">
+        <v>45950</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59" t="s">
+        <v>97</v>
+      </c>
+      <c r="E59" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="1">
+        <v>45950</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" s="1">
+        <v>45954</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE265627-68EA-4A96-B948-1D258018FD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C55731B-AA43-463F-80E0-12FA3C7A205A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="104">
   <si>
     <t>Datum</t>
   </si>
@@ -337,6 +337,18 @@
   </si>
   <si>
     <t>Finish IO unit TX buffer (and check the TXIE bit 💀)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add turbo mode to Sequencer </t>
+  </si>
+  <si>
+    <t>Finish and document sequencer firmware</t>
+  </si>
+  <si>
+    <t>Debug and fix missing reset cycle state in sequencer 💀</t>
+  </si>
+  <si>
+    <t>Debug missing reset cycle state in sequencer 💀</t>
   </si>
 </sst>
 </file>
@@ -715,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E60"/>
+  <dimension ref="B1:E61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -726,7 +738,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -1553,6 +1565,20 @@
       </c>
       <c r="E60" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" s="1">
+        <v>45956</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>103</v>
+      </c>
+      <c r="E61" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1562,7 +1588,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F61"/>
+  <dimension ref="B1:F64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -1573,7 +1599,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>122</v>
+        <v>126.5</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -2429,6 +2455,51 @@
       </c>
       <c r="D61" t="s">
         <v>99</v>
+      </c>
+      <c r="E61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="1">
+        <v>45955</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="s">
+        <v>100</v>
+      </c>
+      <c r="E62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" s="1">
+        <v>45956</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63" t="s">
+        <v>102</v>
+      </c>
+      <c r="E63" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" s="1">
+        <v>45956</v>
+      </c>
+      <c r="C64">
+        <v>1.5</v>
+      </c>
+      <c r="D64" t="s">
+        <v>101</v>
+      </c>
+      <c r="E64" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C55731B-AA43-463F-80E0-12FA3C7A205A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFD59C8-53A6-4963-8119-317058BCA34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="106">
   <si>
     <t>Datum</t>
   </si>
@@ -349,6 +349,12 @@
   </si>
   <si>
     <t>Debug missing reset cycle state in sequencer 💀</t>
+  </si>
+  <si>
+    <t>Debug performance problems of IO unit</t>
+  </si>
+  <si>
+    <t>Improve cycle by clearing hold after next opcode is set</t>
   </si>
 </sst>
 </file>
@@ -1588,7 +1594,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F64"/>
+  <dimension ref="B1:F66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -1599,7 +1605,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>126.5</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -2499,6 +2505,34 @@
         <v>101</v>
       </c>
       <c r="E64" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B65" s="1">
+        <v>45963</v>
+      </c>
+      <c r="C65">
+        <v>2</v>
+      </c>
+      <c r="D65" t="s">
+        <v>104</v>
+      </c>
+      <c r="E65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B66" s="1">
+        <v>45964</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66" t="s">
+        <v>105</v>
+      </c>
+      <c r="E66" t="s">
         <v>24</v>
       </c>
     </row>

--- a/project_mismanagement/zeiten.xlsx
+++ b/project_mismanagement/zeiten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\computer\ax08\project_mismanagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFD59C8-53A6-4963-8119-317058BCA34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BB4FE3-CEAC-437B-8DA9-AA46219D6FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8B2EF68E-96B7-4F72-8440-4EEFFDE0E6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="oliver" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="111">
   <si>
     <t>Datum</t>
   </si>
@@ -355,6 +355,21 @@
   </si>
   <si>
     <t>Improve cycle by clearing hold after next opcode is set</t>
+  </si>
+  <si>
+    <t>Investigate a bug in shift carry</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Debug wrong carry on shift</t>
+  </si>
+  <si>
+    <t>Update sequence to allow for a longer hold pulse</t>
+  </si>
+  <si>
+    <t>ODE 💀</t>
   </si>
 </sst>
 </file>
@@ -733,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605FC15-F497-4A19-9DC6-DDBAF4F9624E}">
-  <dimension ref="B1:E61"/>
+  <dimension ref="B1:E64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -744,7 +759,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>136</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -1584,6 +1599,48 @@
         <v>103</v>
       </c>
       <c r="E61" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="1">
+        <v>45967</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="s">
+        <v>57</v>
+      </c>
+      <c r="E62" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" s="1">
+        <v>45967</v>
+      </c>
+      <c r="C63">
+        <v>0.5</v>
+      </c>
+      <c r="D63" t="s">
+        <v>108</v>
+      </c>
+      <c r="E63" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" s="1">
+        <v>45967</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64" t="s">
+        <v>110</v>
+      </c>
+      <c r="E64" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1594,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED3E0BF-F2BE-451D-97DA-7705BD8F1DBF}">
-  <dimension ref="B1:F66"/>
+  <dimension ref="B1:G70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -1605,7 +1662,7 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C1">
         <f>SUM(C3:C10000)</f>
-        <v>130.5</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -2508,7 +2565,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B65" s="1">
         <v>45963</v>
       </c>
@@ -2522,7 +2579,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B66" s="1">
         <v>45964</v>
       </c>
@@ -2533,6 +2590,71 @@
         <v>105</v>
       </c>
       <c r="E66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="1">
+        <v>45966</v>
+      </c>
+      <c r="C67">
+        <v>0.5</v>
+      </c>
+      <c r="D67" t="s">
+        <v>106</v>
+      </c>
+      <c r="E67" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="1">
+        <v>45967</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68" t="s">
+        <v>57</v>
+      </c>
+      <c r="E68" t="s">
+        <v>32</v>
+      </c>
+      <c r="F68" t="s">
+        <v>51</v>
+      </c>
+      <c r="G68" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="1">
+        <v>45967</v>
+      </c>
+      <c r="C69">
+        <v>0.5</v>
+      </c>
+      <c r="D69" t="s">
+        <v>108</v>
+      </c>
+      <c r="E69" t="s">
+        <v>27</v>
+      </c>
+      <c r="G69" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B70" s="1">
+        <v>45967</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70" t="s">
+        <v>109</v>
+      </c>
+      <c r="E70" t="s">
         <v>24</v>
       </c>
     </row>
